--- a/12604714.xlsx
+++ b/12604714.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af964434807192f7/Documents/cap776^J12604714/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="290" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75E0BC7C-57FA-4F23-B430-529163CB5F61}"/>
+  <xr:revisionPtr revIDLastSave="403" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BEF87174-EA0A-422C-B666-48CEEC0C75C3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="81">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -267,7 +267,22 @@
     <t>today I have 8 class 4lecture 14pratical many class fully exhausted</t>
   </si>
   <si>
-    <t>today I have 4 class 2lecture 2 pratical many class fully exhausted</t>
+    <t xml:space="preserve">today I have 4 class 2lecture 2 pratical </t>
+  </si>
+  <si>
+    <t>today I have 2 class 1 lecture 1 pratical</t>
+  </si>
+  <si>
+    <t>today I have 3 class 2 lecture 1 pratical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">today I have 2 class 2 lecture </t>
+  </si>
+  <si>
+    <t>today I have 5 class 3 lecture 2 pratical</t>
+  </si>
+  <si>
+    <t>today I have 8 class 4 lecture 4 pratical</t>
   </si>
 </sst>
 </file>
@@ -501,13 +516,13 @@
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1020,10 +1035,10 @@
       <c r="E2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="24">
+      <c r="F2" s="28">
         <v>12604714</v>
       </c>
-      <c r="G2" s="24"/>
+      <c r="G2" s="28"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1">
       <c r="A3" s="6" t="s">
@@ -1043,22 +1058,22 @@
       <c r="G3" s="27"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
     </row>
     <row r="5" spans="1:14" ht="41.45">
       <c r="A5" s="7" t="s">
@@ -1886,7 +1901,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="43.5">
+    <row r="23" spans="1:14" ht="28.5">
       <c r="A23" s="8">
         <v>46262</v>
       </c>
@@ -2024,7 +2039,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="43.5">
+    <row r="26" spans="1:14" ht="28.5">
       <c r="A26" s="8">
         <v>46265</v>
       </c>
@@ -2067,239 +2082,469 @@
         <v>55</v>
       </c>
       <c r="N26" s="23" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="43.5">
       <c r="A27" s="8">
         <v>46266</v>
       </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="15"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
+      <c r="B27" s="13">
+        <v>340</v>
+      </c>
+      <c r="C27" s="13">
+        <v>50</v>
+      </c>
+      <c r="D27" s="13">
+        <v>40</v>
+      </c>
+      <c r="E27" s="13">
+        <v>30</v>
+      </c>
+      <c r="F27" s="13">
+        <v>300</v>
+      </c>
+      <c r="G27" s="13">
+        <v>6</v>
+      </c>
+      <c r="H27" s="13">
+        <v>60</v>
+      </c>
+      <c r="I27" s="14">
+        <f t="shared" ref="I27:I28" si="2">IF(SUM(B27:F27,H27)=0,"",SUM(B27:F27,H27))</f>
+        <v>820</v>
+      </c>
+      <c r="J27" s="14">
+        <f t="shared" ref="J27:J28" si="3">IF(I27="","",1440-I27)</f>
+        <v>620</v>
+      </c>
+      <c r="K27" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L27" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M27" s="15" t="s">
+        <v>55</v>
+      </c>
       <c r="N27" s="23" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="43.5">
       <c r="A28" s="8">
         <v>46267</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="14" t="str">
+      <c r="B28" s="13">
+        <v>300</v>
+      </c>
+      <c r="C28" s="13">
+        <v>45</v>
+      </c>
+      <c r="D28" s="13">
+        <v>50</v>
+      </c>
+      <c r="E28" s="13">
+        <v>20</v>
+      </c>
+      <c r="F28" s="13">
+        <v>400</v>
+      </c>
+      <c r="G28" s="13">
+        <v>8</v>
+      </c>
+      <c r="H28" s="13">
+        <v>80</v>
+      </c>
+      <c r="I28" s="14">
+        <f t="shared" si="2"/>
+        <v>895</v>
+      </c>
+      <c r="J28" s="14">
+        <f t="shared" si="3"/>
+        <v>545</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="L28" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M28" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="N28" s="23" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="28.5">
+      <c r="A29" s="8">
+        <v>46268</v>
+      </c>
+      <c r="B29" s="13">
+        <v>340</v>
+      </c>
+      <c r="C29" s="13">
+        <v>40</v>
+      </c>
+      <c r="D29" s="13">
+        <v>45</v>
+      </c>
+      <c r="E29" s="13">
+        <v>40</v>
+      </c>
+      <c r="F29" s="13">
+        <v>180</v>
+      </c>
+      <c r="G29" s="13">
+        <v>3</v>
+      </c>
+      <c r="H29" s="13">
+        <v>180</v>
+      </c>
+      <c r="I29" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="14" t="str">
+        <v>825</v>
+      </c>
+      <c r="J29" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="15"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="23" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
-      <c r="A29" s="12"/>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="14" t="str">
+        <v>615</v>
+      </c>
+      <c r="K29" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L29" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M29" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N29" s="23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="15">
+      <c r="A30" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B30" s="13">
+        <v>320</v>
+      </c>
+      <c r="C30" s="13">
+        <v>50</v>
+      </c>
+      <c r="D30" s="13">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13">
+        <v>50</v>
+      </c>
+      <c r="F30" s="13">
+        <v>200</v>
+      </c>
+      <c r="G30" s="13">
+        <v>4</v>
+      </c>
+      <c r="H30" s="13">
+        <v>120</v>
+      </c>
+      <c r="I30" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="14" t="str">
+        <v>760</v>
+      </c>
+      <c r="J30" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="15"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="16"/>
-    </row>
-    <row r="30" spans="1:14">
-      <c r="A30" s="12"/>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
+        <v>680</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L30" s="15" t="s">
+        <v>54</v>
+      </c>
       <c r="M30" s="15"/>
       <c r="N30" s="16"/>
     </row>
-    <row r="31" spans="1:14">
-      <c r="A31" s="12"/>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="14" t="str">
+    <row r="31" spans="1:14" ht="15">
+      <c r="A31" s="8">
+        <v>46270</v>
+      </c>
+      <c r="B31" s="13">
+        <v>350</v>
+      </c>
+      <c r="C31" s="13">
+        <v>50</v>
+      </c>
+      <c r="D31" s="13">
+        <v>80</v>
+      </c>
+      <c r="E31" s="13">
+        <v>120</v>
+      </c>
+      <c r="F31" s="13">
+        <v>0</v>
+      </c>
+      <c r="G31" s="13">
+        <v>0</v>
+      </c>
+      <c r="H31" s="13">
+        <v>200</v>
+      </c>
+      <c r="I31" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="14" t="str">
+        <v>800</v>
+      </c>
+      <c r="J31" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="15"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
-      <c r="N31" s="16"/>
-    </row>
-    <row r="32" spans="1:14">
-      <c r="A32" s="12"/>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="14" t="str">
+        <v>640</v>
+      </c>
+      <c r="K31" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L31" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="M31" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N31" s="16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="15">
+      <c r="A32" s="8">
+        <v>46271</v>
+      </c>
+      <c r="B32" s="13">
+        <v>300</v>
+      </c>
+      <c r="C32" s="13">
+        <v>60</v>
+      </c>
+      <c r="D32" s="13">
+        <v>100</v>
+      </c>
+      <c r="E32" s="13">
+        <v>100</v>
+      </c>
+      <c r="F32" s="13">
+        <v>0</v>
+      </c>
+      <c r="G32" s="13">
+        <v>0</v>
+      </c>
+      <c r="H32" s="13">
+        <v>160</v>
+      </c>
+      <c r="I32" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J32" s="14" t="str">
+        <v>720</v>
+      </c>
+      <c r="J32" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
-      <c r="N32" s="16"/>
-    </row>
-    <row r="33" spans="1:14">
-      <c r="A33" s="12"/>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="14" t="str">
+        <v>720</v>
+      </c>
+      <c r="K32" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L32" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M32" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="N32" s="16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="28.5">
+      <c r="A33" s="8">
+        <v>46272</v>
+      </c>
+      <c r="B33" s="13">
+        <v>320</v>
+      </c>
+      <c r="C33" s="13">
+        <v>80</v>
+      </c>
+      <c r="D33" s="13">
+        <v>80</v>
+      </c>
+      <c r="E33" s="13">
+        <v>120</v>
+      </c>
+      <c r="F33" s="13">
+        <v>120</v>
+      </c>
+      <c r="G33" s="13">
+        <v>2</v>
+      </c>
+      <c r="H33" s="13">
+        <v>80</v>
+      </c>
+      <c r="I33" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="14" t="str">
+        <v>800</v>
+      </c>
+      <c r="J33" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="15"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
-      <c r="N33" s="16"/>
-    </row>
-    <row r="34" spans="1:14">
-      <c r="A34" s="12"/>
-      <c r="B34" s="13"/>
-      <c r="C34" s="13"/>
-      <c r="D34" s="13"/>
-      <c r="E34" s="13"/>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="14" t="str">
+        <v>640</v>
+      </c>
+      <c r="K33" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L33" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M33" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N33" s="23" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="28.5">
+      <c r="A34" s="8">
+        <v>46273</v>
+      </c>
+      <c r="B34" s="13">
+        <v>300</v>
+      </c>
+      <c r="C34" s="13">
+        <v>80</v>
+      </c>
+      <c r="D34" s="13">
+        <v>100</v>
+      </c>
+      <c r="E34" s="13">
+        <v>40</v>
+      </c>
+      <c r="F34" s="13">
+        <v>250</v>
+      </c>
+      <c r="G34" s="13">
+        <v>5</v>
+      </c>
+      <c r="H34" s="13">
+        <v>120</v>
+      </c>
+      <c r="I34" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="14" t="str">
+        <v>890</v>
+      </c>
+      <c r="J34" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
-      <c r="N34" s="16"/>
-    </row>
-    <row r="35" spans="1:14">
-      <c r="A35" s="12"/>
-      <c r="B35" s="13"/>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="14" t="str">
+        <v>550</v>
+      </c>
+      <c r="K34" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L34" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="M34" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N34" s="23" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="28.5">
+      <c r="A35" s="8">
+        <v>46274</v>
+      </c>
+      <c r="B35" s="13">
+        <v>320</v>
+      </c>
+      <c r="C35" s="13">
+        <v>60</v>
+      </c>
+      <c r="D35" s="13">
+        <v>50</v>
+      </c>
+      <c r="E35" s="13">
+        <v>60</v>
+      </c>
+      <c r="F35" s="13">
+        <v>400</v>
+      </c>
+      <c r="G35" s="13">
+        <v>8</v>
+      </c>
+      <c r="H35" s="13">
+        <v>60</v>
+      </c>
+      <c r="I35" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="14" t="str">
+        <v>950</v>
+      </c>
+      <c r="J35" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="15"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="16"/>
-    </row>
-    <row r="36" spans="1:14">
-      <c r="A36" s="12"/>
-      <c r="B36" s="13"/>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
-      <c r="G36" s="13"/>
-      <c r="H36" s="13"/>
-      <c r="I36" s="14" t="str">
+        <v>490</v>
+      </c>
+      <c r="K35" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="L35" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M35" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N35" s="23" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="28.5">
+      <c r="A36" s="8">
+        <v>46275</v>
+      </c>
+      <c r="B36" s="13">
+        <v>300</v>
+      </c>
+      <c r="C36" s="13">
+        <v>60</v>
+      </c>
+      <c r="D36" s="13">
+        <v>50</v>
+      </c>
+      <c r="E36" s="13">
+        <v>80</v>
+      </c>
+      <c r="F36" s="13">
+        <v>250</v>
+      </c>
+      <c r="G36" s="13">
+        <v>5</v>
+      </c>
+      <c r="H36" s="13">
+        <v>150</v>
+      </c>
+      <c r="I36" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="14" t="str">
+        <v>890</v>
+      </c>
+      <c r="J36" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="16"/>
-    </row>
-    <row r="37" spans="1:14">
-      <c r="A37" s="12"/>
+        <v>550</v>
+      </c>
+      <c r="K36" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L36" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M36" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="N36" s="23" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="15">
+      <c r="A37" s="8">
+        <v>46276</v>
+      </c>
       <c r="B37" s="13"/>
       <c r="C37" s="13"/>
       <c r="D37" s="13"/>
@@ -2320,8 +2565,10 @@
       <c r="M37" s="15"/>
       <c r="N37" s="16"/>
     </row>
-    <row r="38" spans="1:14">
-      <c r="A38" s="12"/>
+    <row r="38" spans="1:14" ht="15">
+      <c r="A38" s="8">
+        <v>46277</v>
+      </c>
       <c r="B38" s="13"/>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
@@ -3034,11 +3281,11 @@
       <c r="G70" s="13"/>
       <c r="H70" s="13"/>
       <c r="I70" s="14" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="4">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="14" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="5">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="15"/>
@@ -3056,11 +3303,11 @@
       <c r="G71" s="13"/>
       <c r="H71" s="13"/>
       <c r="I71" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J71" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K71" s="15"/>
@@ -3078,11 +3325,11 @@
       <c r="G72" s="13"/>
       <c r="H72" s="13"/>
       <c r="I72" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J72" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K72" s="15"/>
@@ -3100,11 +3347,11 @@
       <c r="G73" s="13"/>
       <c r="H73" s="13"/>
       <c r="I73" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J73" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K73" s="15"/>
@@ -3122,11 +3369,11 @@
       <c r="G74" s="13"/>
       <c r="H74" s="13"/>
       <c r="I74" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J74" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K74" s="15"/>
@@ -3144,11 +3391,11 @@
       <c r="G75" s="13"/>
       <c r="H75" s="13"/>
       <c r="I75" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J75" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K75" s="15"/>
@@ -3166,11 +3413,11 @@
       <c r="G76" s="13"/>
       <c r="H76" s="13"/>
       <c r="I76" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J76" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K76" s="15"/>
@@ -3188,11 +3435,11 @@
       <c r="G77" s="13"/>
       <c r="H77" s="13"/>
       <c r="I77" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J77" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K77" s="15"/>
@@ -3210,11 +3457,11 @@
       <c r="G78" s="13"/>
       <c r="H78" s="13"/>
       <c r="I78" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J78" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K78" s="15"/>
@@ -3232,11 +3479,11 @@
       <c r="G79" s="13"/>
       <c r="H79" s="13"/>
       <c r="I79" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J79" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K79" s="15"/>
@@ -3254,11 +3501,11 @@
       <c r="G80" s="13"/>
       <c r="H80" s="13"/>
       <c r="I80" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J80" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K80" s="15"/>
@@ -3276,11 +3523,11 @@
       <c r="G81" s="13"/>
       <c r="H81" s="13"/>
       <c r="I81" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J81" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K81" s="15"/>
@@ -3298,11 +3545,11 @@
       <c r="G82" s="13"/>
       <c r="H82" s="13"/>
       <c r="I82" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J82" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K82" s="15"/>
@@ -3320,11 +3567,11 @@
       <c r="G83" s="13"/>
       <c r="H83" s="13"/>
       <c r="I83" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J83" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K83" s="15"/>
@@ -3342,11 +3589,11 @@
       <c r="G84" s="13"/>
       <c r="H84" s="13"/>
       <c r="I84" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J84" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K84" s="15"/>
@@ -3364,11 +3611,11 @@
       <c r="G85" s="13"/>
       <c r="H85" s="13"/>
       <c r="I85" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J85" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K85" s="15"/>
@@ -3386,11 +3633,11 @@
       <c r="G86" s="13"/>
       <c r="H86" s="13"/>
       <c r="I86" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J86" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K86" s="15"/>
@@ -3408,11 +3655,11 @@
       <c r="G87" s="13"/>
       <c r="H87" s="13"/>
       <c r="I87" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J87" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K87" s="15"/>
@@ -3430,11 +3677,11 @@
       <c r="G88" s="13"/>
       <c r="H88" s="13"/>
       <c r="I88" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J88" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K88" s="15"/>
@@ -3452,11 +3699,11 @@
       <c r="G89" s="13"/>
       <c r="H89" s="13"/>
       <c r="I89" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J89" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K89" s="15"/>
@@ -3474,11 +3721,11 @@
       <c r="G90" s="13"/>
       <c r="H90" s="13"/>
       <c r="I90" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J90" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K90" s="15"/>
@@ -3496,11 +3743,11 @@
       <c r="G91" s="13"/>
       <c r="H91" s="13"/>
       <c r="I91" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J91" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K91" s="15"/>
@@ -3518,11 +3765,11 @@
       <c r="G92" s="13"/>
       <c r="H92" s="13"/>
       <c r="I92" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J92" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K92" s="15"/>
@@ -3540,11 +3787,11 @@
       <c r="G93" s="13"/>
       <c r="H93" s="13"/>
       <c r="I93" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J93" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K93" s="15"/>
@@ -3562,11 +3809,11 @@
       <c r="G94" s="13"/>
       <c r="H94" s="13"/>
       <c r="I94" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J94" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K94" s="15"/>
@@ -3584,11 +3831,11 @@
       <c r="G95" s="13"/>
       <c r="H95" s="13"/>
       <c r="I95" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J95" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K95" s="15"/>
@@ -3606,11 +3853,11 @@
       <c r="G96" s="13"/>
       <c r="H96" s="13"/>
       <c r="I96" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J96" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K96" s="15"/>
@@ -3628,11 +3875,11 @@
       <c r="G97" s="13"/>
       <c r="H97" s="13"/>
       <c r="I97" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J97" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K97" s="15"/>
@@ -3650,11 +3897,11 @@
       <c r="G98" s="13"/>
       <c r="H98" s="13"/>
       <c r="I98" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J98" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K98" s="15"/>
@@ -3672,11 +3919,11 @@
       <c r="G99" s="13"/>
       <c r="H99" s="13"/>
       <c r="I99" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J99" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K99" s="15"/>
@@ -3694,11 +3941,11 @@
       <c r="G100" s="13"/>
       <c r="H100" s="13"/>
       <c r="I100" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J100" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K100" s="15"/>
@@ -3716,11 +3963,11 @@
       <c r="G101" s="13"/>
       <c r="H101" s="13"/>
       <c r="I101" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J101" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K101" s="15"/>
@@ -3738,11 +3985,11 @@
       <c r="G102" s="13"/>
       <c r="H102" s="13"/>
       <c r="I102" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J102" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K102" s="15"/>
@@ -3760,11 +4007,11 @@
       <c r="G103" s="13"/>
       <c r="H103" s="13"/>
       <c r="I103" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J103" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K103" s="15"/>
@@ -3782,11 +4029,11 @@
       <c r="G104" s="13"/>
       <c r="H104" s="13"/>
       <c r="I104" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J104" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K104" s="15"/>
@@ -3804,11 +4051,11 @@
       <c r="G105" s="13"/>
       <c r="H105" s="13"/>
       <c r="I105" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J105" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K105" s="15"/>
@@ -3826,11 +4073,11 @@
       <c r="G106" s="13"/>
       <c r="H106" s="13"/>
       <c r="I106" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J106" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K106" s="15"/>
@@ -3848,11 +4095,11 @@
       <c r="G107" s="13"/>
       <c r="H107" s="13"/>
       <c r="I107" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J107" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K107" s="15"/>
@@ -3870,11 +4117,11 @@
       <c r="G108" s="13"/>
       <c r="H108" s="13"/>
       <c r="I108" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J108" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K108" s="15"/>
@@ -3892,11 +4139,11 @@
       <c r="G109" s="13"/>
       <c r="H109" s="13"/>
       <c r="I109" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J109" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K109" s="15"/>
@@ -3914,11 +4161,11 @@
       <c r="G110" s="13"/>
       <c r="H110" s="13"/>
       <c r="I110" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J110" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K110" s="15"/>
@@ -3936,11 +4183,11 @@
       <c r="G111" s="13"/>
       <c r="H111" s="13"/>
       <c r="I111" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J111" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K111" s="15"/>
@@ -3958,11 +4205,11 @@
       <c r="G112" s="13"/>
       <c r="H112" s="13"/>
       <c r="I112" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J112" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K112" s="15"/>
@@ -3980,11 +4227,11 @@
       <c r="G113" s="13"/>
       <c r="H113" s="13"/>
       <c r="I113" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J113" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K113" s="15"/>
@@ -4002,11 +4249,11 @@
       <c r="G114" s="13"/>
       <c r="H114" s="13"/>
       <c r="I114" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J114" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K114" s="15"/>
@@ -4024,11 +4271,11 @@
       <c r="G115" s="13"/>
       <c r="H115" s="13"/>
       <c r="I115" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J115" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K115" s="15"/>
@@ -4046,11 +4293,11 @@
       <c r="G116" s="13"/>
       <c r="H116" s="13"/>
       <c r="I116" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J116" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K116" s="15"/>
@@ -4068,11 +4315,11 @@
       <c r="G117" s="13"/>
       <c r="H117" s="13"/>
       <c r="I117" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J117" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K117" s="15"/>
@@ -4090,11 +4337,11 @@
       <c r="G118" s="13"/>
       <c r="H118" s="13"/>
       <c r="I118" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J118" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K118" s="15"/>
@@ -4112,11 +4359,11 @@
       <c r="G119" s="13"/>
       <c r="H119" s="13"/>
       <c r="I119" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J119" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K119" s="15"/>
@@ -4134,11 +4381,11 @@
       <c r="G120" s="13"/>
       <c r="H120" s="13"/>
       <c r="I120" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J120" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K120" s="15"/>
@@ -4156,11 +4403,11 @@
       <c r="G121" s="13"/>
       <c r="H121" s="13"/>
       <c r="I121" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J121" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K121" s="15"/>
@@ -4178,11 +4425,11 @@
       <c r="G122" s="13"/>
       <c r="H122" s="13"/>
       <c r="I122" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J122" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K122" s="15"/>
@@ -4200,11 +4447,11 @@
       <c r="G123" s="13"/>
       <c r="H123" s="13"/>
       <c r="I123" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J123" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K123" s="15"/>
@@ -4222,11 +4469,11 @@
       <c r="G124" s="13"/>
       <c r="H124" s="13"/>
       <c r="I124" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J124" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K124" s="15"/>
@@ -4244,11 +4491,11 @@
       <c r="G125" s="13"/>
       <c r="H125" s="13"/>
       <c r="I125" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J125" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K125" s="15"/>
@@ -4266,11 +4513,11 @@
       <c r="G126" s="13"/>
       <c r="H126" s="13"/>
       <c r="I126" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J126" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K126" s="15"/>
@@ -4288,11 +4535,11 @@
       <c r="G127" s="13"/>
       <c r="H127" s="13"/>
       <c r="I127" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J127" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K127" s="15"/>
@@ -4310,11 +4557,11 @@
       <c r="G128" s="13"/>
       <c r="H128" s="13"/>
       <c r="I128" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J128" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K128" s="15"/>
@@ -4332,11 +4579,11 @@
       <c r="G129" s="13"/>
       <c r="H129" s="13"/>
       <c r="I129" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J129" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K129" s="15"/>
@@ -4354,11 +4601,11 @@
       <c r="G130" s="13"/>
       <c r="H130" s="13"/>
       <c r="I130" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J130" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K130" s="15"/>
@@ -4376,11 +4623,11 @@
       <c r="G131" s="13"/>
       <c r="H131" s="13"/>
       <c r="I131" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J131" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K131" s="15"/>
@@ -4398,11 +4645,11 @@
       <c r="G132" s="13"/>
       <c r="H132" s="13"/>
       <c r="I132" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J132" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K132" s="15"/>
@@ -4420,11 +4667,11 @@
       <c r="G133" s="13"/>
       <c r="H133" s="13"/>
       <c r="I133" s="14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J133" s="14" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K133" s="15"/>
@@ -4442,11 +4689,11 @@
       <c r="G134" s="13"/>
       <c r="H134" s="13"/>
       <c r="I134" s="14" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="6">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="14" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="7">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="15"/>
@@ -4464,11 +4711,11 @@
       <c r="G135" s="13"/>
       <c r="H135" s="13"/>
       <c r="I135" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J135" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K135" s="15"/>
@@ -4486,11 +4733,11 @@
       <c r="G136" s="13"/>
       <c r="H136" s="13"/>
       <c r="I136" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J136" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K136" s="15"/>
@@ -4508,11 +4755,11 @@
       <c r="G137" s="13"/>
       <c r="H137" s="13"/>
       <c r="I137" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J137" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K137" s="15"/>
@@ -4530,11 +4777,11 @@
       <c r="G138" s="13"/>
       <c r="H138" s="13"/>
       <c r="I138" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J138" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K138" s="15"/>
@@ -4552,11 +4799,11 @@
       <c r="G139" s="13"/>
       <c r="H139" s="13"/>
       <c r="I139" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J139" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K139" s="15"/>
@@ -4574,11 +4821,11 @@
       <c r="G140" s="13"/>
       <c r="H140" s="13"/>
       <c r="I140" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J140" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K140" s="15"/>
@@ -4596,11 +4843,11 @@
       <c r="G141" s="13"/>
       <c r="H141" s="13"/>
       <c r="I141" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J141" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K141" s="15"/>
@@ -4618,11 +4865,11 @@
       <c r="G142" s="13"/>
       <c r="H142" s="13"/>
       <c r="I142" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J142" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K142" s="15"/>
@@ -4640,11 +4887,11 @@
       <c r="G143" s="13"/>
       <c r="H143" s="13"/>
       <c r="I143" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J143" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K143" s="15"/>
@@ -4662,11 +4909,11 @@
       <c r="G144" s="13"/>
       <c r="H144" s="13"/>
       <c r="I144" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J144" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K144" s="15"/>
@@ -4684,11 +4931,11 @@
       <c r="G145" s="13"/>
       <c r="H145" s="13"/>
       <c r="I145" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J145" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K145" s="15"/>
@@ -4706,11 +4953,11 @@
       <c r="G146" s="13"/>
       <c r="H146" s="13"/>
       <c r="I146" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J146" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K146" s="15"/>
@@ -4728,11 +4975,11 @@
       <c r="G147" s="13"/>
       <c r="H147" s="13"/>
       <c r="I147" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J147" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K147" s="15"/>
@@ -4750,11 +4997,11 @@
       <c r="G148" s="13"/>
       <c r="H148" s="13"/>
       <c r="I148" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J148" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K148" s="15"/>
@@ -4772,11 +5019,11 @@
       <c r="G149" s="13"/>
       <c r="H149" s="13"/>
       <c r="I149" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J149" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K149" s="15"/>
@@ -4794,11 +5041,11 @@
       <c r="G150" s="13"/>
       <c r="H150" s="13"/>
       <c r="I150" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J150" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K150" s="15"/>
@@ -4816,11 +5063,11 @@
       <c r="G151" s="13"/>
       <c r="H151" s="13"/>
       <c r="I151" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J151" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K151" s="15"/>
@@ -4838,11 +5085,11 @@
       <c r="G152" s="13"/>
       <c r="H152" s="13"/>
       <c r="I152" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J152" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K152" s="15"/>
@@ -4860,11 +5107,11 @@
       <c r="G153" s="13"/>
       <c r="H153" s="13"/>
       <c r="I153" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J153" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K153" s="15"/>
@@ -4882,11 +5129,11 @@
       <c r="G154" s="13"/>
       <c r="H154" s="13"/>
       <c r="I154" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J154" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K154" s="15"/>
@@ -4904,11 +5151,11 @@
       <c r="G155" s="13"/>
       <c r="H155" s="13"/>
       <c r="I155" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J155" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K155" s="15"/>
@@ -4926,11 +5173,11 @@
       <c r="G156" s="13"/>
       <c r="H156" s="13"/>
       <c r="I156" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J156" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K156" s="15"/>
@@ -4948,11 +5195,11 @@
       <c r="G157" s="13"/>
       <c r="H157" s="13"/>
       <c r="I157" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J157" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K157" s="15"/>
@@ -4970,11 +5217,11 @@
       <c r="G158" s="13"/>
       <c r="H158" s="13"/>
       <c r="I158" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J158" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K158" s="15"/>
@@ -4992,11 +5239,11 @@
       <c r="G159" s="13"/>
       <c r="H159" s="13"/>
       <c r="I159" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J159" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K159" s="15"/>
@@ -5014,11 +5261,11 @@
       <c r="G160" s="13"/>
       <c r="H160" s="13"/>
       <c r="I160" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J160" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K160" s="15"/>
@@ -5036,11 +5283,11 @@
       <c r="G161" s="13"/>
       <c r="H161" s="13"/>
       <c r="I161" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J161" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K161" s="15"/>
@@ -5058,11 +5305,11 @@
       <c r="G162" s="13"/>
       <c r="H162" s="13"/>
       <c r="I162" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J162" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K162" s="15"/>
@@ -5080,11 +5327,11 @@
       <c r="G163" s="13"/>
       <c r="H163" s="13"/>
       <c r="I163" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J163" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K163" s="15"/>
@@ -5102,11 +5349,11 @@
       <c r="G164" s="13"/>
       <c r="H164" s="13"/>
       <c r="I164" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J164" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K164" s="15"/>
@@ -5124,11 +5371,11 @@
       <c r="G165" s="13"/>
       <c r="H165" s="13"/>
       <c r="I165" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J165" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K165" s="15"/>
@@ -5146,11 +5393,11 @@
       <c r="G166" s="13"/>
       <c r="H166" s="13"/>
       <c r="I166" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J166" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K166" s="15"/>
@@ -5168,11 +5415,11 @@
       <c r="G167" s="13"/>
       <c r="H167" s="13"/>
       <c r="I167" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J167" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K167" s="15"/>
@@ -5190,11 +5437,11 @@
       <c r="G168" s="13"/>
       <c r="H168" s="13"/>
       <c r="I168" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J168" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K168" s="15"/>
@@ -5212,11 +5459,11 @@
       <c r="G169" s="13"/>
       <c r="H169" s="13"/>
       <c r="I169" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J169" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K169" s="15"/>
@@ -5234,11 +5481,11 @@
       <c r="G170" s="13"/>
       <c r="H170" s="13"/>
       <c r="I170" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J170" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K170" s="15"/>
@@ -5256,11 +5503,11 @@
       <c r="G171" s="13"/>
       <c r="H171" s="13"/>
       <c r="I171" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J171" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K171" s="15"/>
@@ -5278,11 +5525,11 @@
       <c r="G172" s="13"/>
       <c r="H172" s="13"/>
       <c r="I172" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J172" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K172" s="15"/>
@@ -5300,11 +5547,11 @@
       <c r="G173" s="13"/>
       <c r="H173" s="13"/>
       <c r="I173" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J173" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K173" s="15"/>
@@ -5322,11 +5569,11 @@
       <c r="G174" s="13"/>
       <c r="H174" s="13"/>
       <c r="I174" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J174" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K174" s="15"/>
@@ -5344,11 +5591,11 @@
       <c r="G175" s="13"/>
       <c r="H175" s="13"/>
       <c r="I175" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J175" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K175" s="15"/>
@@ -5366,11 +5613,11 @@
       <c r="G176" s="13"/>
       <c r="H176" s="13"/>
       <c r="I176" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J176" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K176" s="15"/>
@@ -5388,11 +5635,11 @@
       <c r="G177" s="13"/>
       <c r="H177" s="13"/>
       <c r="I177" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J177" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K177" s="15"/>
@@ -5410,11 +5657,11 @@
       <c r="G178" s="13"/>
       <c r="H178" s="13"/>
       <c r="I178" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J178" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K178" s="15"/>
@@ -5432,11 +5679,11 @@
       <c r="G179" s="13"/>
       <c r="H179" s="13"/>
       <c r="I179" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J179" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K179" s="15"/>
@@ -5454,11 +5701,11 @@
       <c r="G180" s="13"/>
       <c r="H180" s="13"/>
       <c r="I180" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J180" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K180" s="15"/>
@@ -5476,11 +5723,11 @@
       <c r="G181" s="13"/>
       <c r="H181" s="13"/>
       <c r="I181" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J181" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K181" s="15"/>
@@ -5498,11 +5745,11 @@
       <c r="G182" s="13"/>
       <c r="H182" s="13"/>
       <c r="I182" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J182" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K182" s="15"/>
@@ -5520,11 +5767,11 @@
       <c r="G183" s="13"/>
       <c r="H183" s="13"/>
       <c r="I183" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J183" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K183" s="15"/>
@@ -5542,11 +5789,11 @@
       <c r="G184" s="13"/>
       <c r="H184" s="13"/>
       <c r="I184" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J184" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K184" s="15"/>
@@ -5564,11 +5811,11 @@
       <c r="G185" s="13"/>
       <c r="H185" s="13"/>
       <c r="I185" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J185" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K185" s="15"/>
@@ -5586,11 +5833,11 @@
       <c r="G186" s="13"/>
       <c r="H186" s="13"/>
       <c r="I186" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J186" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K186" s="15"/>
@@ -5608,11 +5855,11 @@
       <c r="G187" s="13"/>
       <c r="H187" s="13"/>
       <c r="I187" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J187" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K187" s="15"/>
@@ -5630,11 +5877,11 @@
       <c r="G188" s="13"/>
       <c r="H188" s="13"/>
       <c r="I188" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J188" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K188" s="15"/>
@@ -5652,11 +5899,11 @@
       <c r="G189" s="13"/>
       <c r="H189" s="13"/>
       <c r="I189" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J189" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K189" s="15"/>
@@ -5674,11 +5921,11 @@
       <c r="G190" s="13"/>
       <c r="H190" s="13"/>
       <c r="I190" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J190" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K190" s="15"/>
@@ -5696,11 +5943,11 @@
       <c r="G191" s="13"/>
       <c r="H191" s="13"/>
       <c r="I191" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J191" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K191" s="15"/>
@@ -5718,11 +5965,11 @@
       <c r="G192" s="13"/>
       <c r="H192" s="13"/>
       <c r="I192" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J192" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K192" s="15"/>
@@ -5740,11 +5987,11 @@
       <c r="G193" s="13"/>
       <c r="H193" s="13"/>
       <c r="I193" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J193" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K193" s="15"/>
@@ -5762,11 +6009,11 @@
       <c r="G194" s="13"/>
       <c r="H194" s="13"/>
       <c r="I194" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J194" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K194" s="15"/>
@@ -5784,11 +6031,11 @@
       <c r="G195" s="13"/>
       <c r="H195" s="13"/>
       <c r="I195" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J195" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K195" s="15"/>
@@ -5806,11 +6053,11 @@
       <c r="G196" s="13"/>
       <c r="H196" s="13"/>
       <c r="I196" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J196" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K196" s="15"/>
@@ -5828,11 +6075,11 @@
       <c r="G197" s="13"/>
       <c r="H197" s="13"/>
       <c r="I197" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J197" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K197" s="15"/>
@@ -5850,11 +6097,11 @@
       <c r="G198" s="13"/>
       <c r="H198" s="13"/>
       <c r="I198" s="14" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="8">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="14" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="9">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="15"/>
@@ -5872,11 +6119,11 @@
       <c r="G199" s="13"/>
       <c r="H199" s="13"/>
       <c r="I199" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J199" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K199" s="15"/>
@@ -5894,11 +6141,11 @@
       <c r="G200" s="13"/>
       <c r="H200" s="13"/>
       <c r="I200" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J200" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K200" s="15"/>
@@ -5916,11 +6163,11 @@
       <c r="G201" s="13"/>
       <c r="H201" s="13"/>
       <c r="I201" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J201" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K201" s="15"/>
@@ -5938,11 +6185,11 @@
       <c r="G202" s="13"/>
       <c r="H202" s="13"/>
       <c r="I202" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J202" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K202" s="15"/>
@@ -5960,11 +6207,11 @@
       <c r="G203" s="13"/>
       <c r="H203" s="13"/>
       <c r="I203" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J203" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K203" s="15"/>
@@ -5982,11 +6229,11 @@
       <c r="G204" s="13"/>
       <c r="H204" s="13"/>
       <c r="I204" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J204" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K204" s="15"/>
@@ -6004,11 +6251,11 @@
       <c r="G205" s="13"/>
       <c r="H205" s="13"/>
       <c r="I205" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J205" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K205" s="15"/>
@@ -6026,11 +6273,11 @@
       <c r="G206" s="13"/>
       <c r="H206" s="13"/>
       <c r="I206" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J206" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K206" s="15"/>
@@ -6048,11 +6295,11 @@
       <c r="G207" s="13"/>
       <c r="H207" s="13"/>
       <c r="I207" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J207" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K207" s="15"/>
@@ -6070,11 +6317,11 @@
       <c r="G208" s="13"/>
       <c r="H208" s="13"/>
       <c r="I208" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J208" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K208" s="15"/>
@@ -6092,11 +6339,11 @@
       <c r="G209" s="13"/>
       <c r="H209" s="13"/>
       <c r="I209" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J209" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K209" s="15"/>
@@ -6114,11 +6361,11 @@
       <c r="G210" s="13"/>
       <c r="H210" s="13"/>
       <c r="I210" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J210" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K210" s="15"/>
@@ -6136,11 +6383,11 @@
       <c r="G211" s="13"/>
       <c r="H211" s="13"/>
       <c r="I211" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J211" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K211" s="15"/>
@@ -6158,11 +6405,11 @@
       <c r="G212" s="13"/>
       <c r="H212" s="13"/>
       <c r="I212" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J212" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K212" s="15"/>
@@ -6180,11 +6427,11 @@
       <c r="G213" s="13"/>
       <c r="H213" s="13"/>
       <c r="I213" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J213" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K213" s="15"/>
@@ -6202,11 +6449,11 @@
       <c r="G214" s="13"/>
       <c r="H214" s="13"/>
       <c r="I214" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J214" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K214" s="15"/>
@@ -6224,11 +6471,11 @@
       <c r="G215" s="13"/>
       <c r="H215" s="13"/>
       <c r="I215" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J215" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K215" s="15"/>
@@ -6246,11 +6493,11 @@
       <c r="G216" s="13"/>
       <c r="H216" s="13"/>
       <c r="I216" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J216" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K216" s="15"/>
@@ -6268,11 +6515,11 @@
       <c r="G217" s="13"/>
       <c r="H217" s="13"/>
       <c r="I217" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J217" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K217" s="15"/>
@@ -6290,11 +6537,11 @@
       <c r="G218" s="13"/>
       <c r="H218" s="13"/>
       <c r="I218" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J218" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K218" s="15"/>
@@ -6312,11 +6559,11 @@
       <c r="G219" s="13"/>
       <c r="H219" s="13"/>
       <c r="I219" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J219" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K219" s="15"/>
@@ -6334,11 +6581,11 @@
       <c r="G220" s="13"/>
       <c r="H220" s="13"/>
       <c r="I220" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J220" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K220" s="15"/>
@@ -6356,11 +6603,11 @@
       <c r="G221" s="13"/>
       <c r="H221" s="13"/>
       <c r="I221" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J221" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K221" s="15"/>
@@ -6378,11 +6625,11 @@
       <c r="G222" s="13"/>
       <c r="H222" s="13"/>
       <c r="I222" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J222" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K222" s="15"/>
@@ -6400,11 +6647,11 @@
       <c r="G223" s="13"/>
       <c r="H223" s="13"/>
       <c r="I223" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J223" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K223" s="15"/>
@@ -6422,11 +6669,11 @@
       <c r="G224" s="13"/>
       <c r="H224" s="13"/>
       <c r="I224" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J224" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K224" s="15"/>
@@ -6444,11 +6691,11 @@
       <c r="G225" s="13"/>
       <c r="H225" s="13"/>
       <c r="I225" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J225" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K225" s="15"/>
@@ -6466,11 +6713,11 @@
       <c r="G226" s="13"/>
       <c r="H226" s="13"/>
       <c r="I226" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J226" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K226" s="15"/>
@@ -6488,11 +6735,11 @@
       <c r="G227" s="13"/>
       <c r="H227" s="13"/>
       <c r="I227" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J227" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K227" s="15"/>
@@ -6510,11 +6757,11 @@
       <c r="G228" s="13"/>
       <c r="H228" s="13"/>
       <c r="I228" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J228" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K228" s="15"/>
@@ -6532,11 +6779,11 @@
       <c r="G229" s="13"/>
       <c r="H229" s="13"/>
       <c r="I229" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J229" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K229" s="15"/>
@@ -6554,11 +6801,11 @@
       <c r="G230" s="13"/>
       <c r="H230" s="13"/>
       <c r="I230" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J230" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K230" s="15"/>
@@ -6576,11 +6823,11 @@
       <c r="G231" s="13"/>
       <c r="H231" s="13"/>
       <c r="I231" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J231" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K231" s="15"/>
@@ -6598,11 +6845,11 @@
       <c r="G232" s="13"/>
       <c r="H232" s="13"/>
       <c r="I232" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J232" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K232" s="15"/>
@@ -6620,11 +6867,11 @@
       <c r="G233" s="13"/>
       <c r="H233" s="13"/>
       <c r="I233" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J233" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K233" s="15"/>
@@ -6642,11 +6889,11 @@
       <c r="G234" s="13"/>
       <c r="H234" s="13"/>
       <c r="I234" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J234" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K234" s="15"/>
@@ -6664,11 +6911,11 @@
       <c r="G235" s="13"/>
       <c r="H235" s="13"/>
       <c r="I235" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J235" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K235" s="15"/>
@@ -6686,11 +6933,11 @@
       <c r="G236" s="13"/>
       <c r="H236" s="13"/>
       <c r="I236" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J236" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K236" s="15"/>
@@ -6708,11 +6955,11 @@
       <c r="G237" s="13"/>
       <c r="H237" s="13"/>
       <c r="I237" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J237" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K237" s="15"/>
@@ -6730,11 +6977,11 @@
       <c r="G238" s="13"/>
       <c r="H238" s="13"/>
       <c r="I238" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J238" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K238" s="15"/>
@@ -6752,11 +6999,11 @@
       <c r="G239" s="13"/>
       <c r="H239" s="13"/>
       <c r="I239" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J239" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K239" s="15"/>
@@ -6774,11 +7021,11 @@
       <c r="G240" s="13"/>
       <c r="H240" s="13"/>
       <c r="I240" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J240" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K240" s="15"/>
@@ -6796,11 +7043,11 @@
       <c r="G241" s="13"/>
       <c r="H241" s="13"/>
       <c r="I241" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J241" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K241" s="15"/>
@@ -6818,11 +7065,11 @@
       <c r="G242" s="13"/>
       <c r="H242" s="13"/>
       <c r="I242" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J242" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K242" s="15"/>
@@ -6840,11 +7087,11 @@
       <c r="G243" s="13"/>
       <c r="H243" s="13"/>
       <c r="I243" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J243" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K243" s="15"/>
@@ -6862,11 +7109,11 @@
       <c r="G244" s="13"/>
       <c r="H244" s="13"/>
       <c r="I244" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J244" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K244" s="15"/>
@@ -6884,11 +7131,11 @@
       <c r="G245" s="13"/>
       <c r="H245" s="13"/>
       <c r="I245" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J245" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K245" s="15"/>
@@ -6906,11 +7153,11 @@
       <c r="G246" s="13"/>
       <c r="H246" s="13"/>
       <c r="I246" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J246" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K246" s="15"/>
@@ -6928,11 +7175,11 @@
       <c r="G247" s="13"/>
       <c r="H247" s="13"/>
       <c r="I247" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J247" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K247" s="15"/>
@@ -6950,11 +7197,11 @@
       <c r="G248" s="13"/>
       <c r="H248" s="13"/>
       <c r="I248" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J248" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K248" s="15"/>
@@ -6972,11 +7219,11 @@
       <c r="G249" s="13"/>
       <c r="H249" s="13"/>
       <c r="I249" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J249" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K249" s="15"/>
@@ -6994,11 +7241,11 @@
       <c r="G250" s="13"/>
       <c r="H250" s="13"/>
       <c r="I250" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J250" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K250" s="15"/>
@@ -7016,11 +7263,11 @@
       <c r="G251" s="13"/>
       <c r="H251" s="13"/>
       <c r="I251" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J251" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K251" s="15"/>
@@ -7038,11 +7285,11 @@
       <c r="G252" s="13"/>
       <c r="H252" s="13"/>
       <c r="I252" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J252" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K252" s="15"/>
@@ -7060,11 +7307,11 @@
       <c r="G253" s="13"/>
       <c r="H253" s="13"/>
       <c r="I253" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J253" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K253" s="15"/>
@@ -7082,11 +7329,11 @@
       <c r="G254" s="13"/>
       <c r="H254" s="13"/>
       <c r="I254" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J254" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K254" s="15"/>
@@ -7104,11 +7351,11 @@
       <c r="G255" s="13"/>
       <c r="H255" s="13"/>
       <c r="I255" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J255" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K255" s="15"/>
@@ -7126,11 +7373,11 @@
       <c r="G256" s="13"/>
       <c r="H256" s="13"/>
       <c r="I256" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J256" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K256" s="15"/>
@@ -7148,11 +7395,11 @@
       <c r="G257" s="13"/>
       <c r="H257" s="13"/>
       <c r="I257" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J257" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K257" s="15"/>
@@ -7170,11 +7417,11 @@
       <c r="G258" s="13"/>
       <c r="H258" s="13"/>
       <c r="I258" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J258" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K258" s="15"/>
@@ -7192,11 +7439,11 @@
       <c r="G259" s="13"/>
       <c r="H259" s="13"/>
       <c r="I259" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J259" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K259" s="15"/>
@@ -7214,11 +7461,11 @@
       <c r="G260" s="13"/>
       <c r="H260" s="13"/>
       <c r="I260" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J260" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K260" s="15"/>
@@ -7236,11 +7483,11 @@
       <c r="G261" s="13"/>
       <c r="H261" s="13"/>
       <c r="I261" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J261" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K261" s="15"/>
@@ -7258,11 +7505,11 @@
       <c r="G262" s="13"/>
       <c r="H262" s="13"/>
       <c r="I262" s="14" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="10">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="14" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="11">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="15"/>
@@ -7280,11 +7527,11 @@
       <c r="G263" s="13"/>
       <c r="H263" s="13"/>
       <c r="I263" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J263" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K263" s="15"/>
@@ -7302,11 +7549,11 @@
       <c r="G264" s="13"/>
       <c r="H264" s="13"/>
       <c r="I264" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J264" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K264" s="15"/>
@@ -7324,11 +7571,11 @@
       <c r="G265" s="13"/>
       <c r="H265" s="13"/>
       <c r="I265" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J265" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K265" s="15"/>
@@ -7346,11 +7593,11 @@
       <c r="G266" s="13"/>
       <c r="H266" s="13"/>
       <c r="I266" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J266" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K266" s="15"/>
@@ -7368,11 +7615,11 @@
       <c r="G267" s="13"/>
       <c r="H267" s="13"/>
       <c r="I267" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J267" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K267" s="15"/>
@@ -7390,11 +7637,11 @@
       <c r="G268" s="13"/>
       <c r="H268" s="13"/>
       <c r="I268" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J268" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K268" s="15"/>
@@ -7412,11 +7659,11 @@
       <c r="G269" s="13"/>
       <c r="H269" s="13"/>
       <c r="I269" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J269" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K269" s="15"/>
@@ -7434,11 +7681,11 @@
       <c r="G270" s="13"/>
       <c r="H270" s="13"/>
       <c r="I270" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J270" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K270" s="15"/>
@@ -7456,11 +7703,11 @@
       <c r="G271" s="13"/>
       <c r="H271" s="13"/>
       <c r="I271" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J271" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K271" s="15"/>
@@ -7478,11 +7725,11 @@
       <c r="G272" s="13"/>
       <c r="H272" s="13"/>
       <c r="I272" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J272" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K272" s="15"/>
@@ -7500,11 +7747,11 @@
       <c r="G273" s="13"/>
       <c r="H273" s="13"/>
       <c r="I273" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J273" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K273" s="15"/>
@@ -7522,11 +7769,11 @@
       <c r="G274" s="13"/>
       <c r="H274" s="13"/>
       <c r="I274" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J274" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K274" s="15"/>
@@ -7544,11 +7791,11 @@
       <c r="G275" s="13"/>
       <c r="H275" s="13"/>
       <c r="I275" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J275" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K275" s="15"/>
@@ -7566,11 +7813,11 @@
       <c r="G276" s="13"/>
       <c r="H276" s="13"/>
       <c r="I276" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J276" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K276" s="15"/>
@@ -7588,11 +7835,11 @@
       <c r="G277" s="13"/>
       <c r="H277" s="13"/>
       <c r="I277" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J277" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K277" s="15"/>
@@ -7610,11 +7857,11 @@
       <c r="G278" s="13"/>
       <c r="H278" s="13"/>
       <c r="I278" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J278" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K278" s="15"/>
@@ -7632,11 +7879,11 @@
       <c r="G279" s="13"/>
       <c r="H279" s="13"/>
       <c r="I279" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J279" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K279" s="15"/>
@@ -7654,11 +7901,11 @@
       <c r="G280" s="13"/>
       <c r="H280" s="13"/>
       <c r="I280" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J280" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K280" s="15"/>
@@ -7676,11 +7923,11 @@
       <c r="G281" s="13"/>
       <c r="H281" s="13"/>
       <c r="I281" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J281" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K281" s="15"/>
@@ -7698,11 +7945,11 @@
       <c r="G282" s="13"/>
       <c r="H282" s="13"/>
       <c r="I282" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J282" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K282" s="15"/>
@@ -7720,11 +7967,11 @@
       <c r="G283" s="13"/>
       <c r="H283" s="13"/>
       <c r="I283" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J283" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K283" s="15"/>
@@ -7742,11 +7989,11 @@
       <c r="G284" s="13"/>
       <c r="H284" s="13"/>
       <c r="I284" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J284" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K284" s="15"/>
@@ -7764,11 +8011,11 @@
       <c r="G285" s="13"/>
       <c r="H285" s="13"/>
       <c r="I285" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J285" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K285" s="15"/>
@@ -7786,11 +8033,11 @@
       <c r="G286" s="13"/>
       <c r="H286" s="13"/>
       <c r="I286" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J286" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K286" s="15"/>
@@ -7808,11 +8055,11 @@
       <c r="G287" s="13"/>
       <c r="H287" s="13"/>
       <c r="I287" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J287" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K287" s="15"/>
@@ -7830,11 +8077,11 @@
       <c r="G288" s="13"/>
       <c r="H288" s="13"/>
       <c r="I288" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J288" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K288" s="15"/>
@@ -7852,11 +8099,11 @@
       <c r="G289" s="13"/>
       <c r="H289" s="13"/>
       <c r="I289" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J289" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K289" s="15"/>
@@ -7874,11 +8121,11 @@
       <c r="G290" s="13"/>
       <c r="H290" s="13"/>
       <c r="I290" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J290" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K290" s="15"/>
@@ -7896,11 +8143,11 @@
       <c r="G291" s="13"/>
       <c r="H291" s="13"/>
       <c r="I291" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J291" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K291" s="15"/>
@@ -7918,11 +8165,11 @@
       <c r="G292" s="13"/>
       <c r="H292" s="13"/>
       <c r="I292" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J292" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K292" s="15"/>
@@ -7940,11 +8187,11 @@
       <c r="G293" s="13"/>
       <c r="H293" s="13"/>
       <c r="I293" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J293" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K293" s="15"/>
@@ -7962,11 +8209,11 @@
       <c r="G294" s="13"/>
       <c r="H294" s="13"/>
       <c r="I294" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J294" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K294" s="15"/>
@@ -7984,11 +8231,11 @@
       <c r="G295" s="13"/>
       <c r="H295" s="13"/>
       <c r="I295" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J295" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K295" s="15"/>
@@ -8006,11 +8253,11 @@
       <c r="G296" s="13"/>
       <c r="H296" s="13"/>
       <c r="I296" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J296" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K296" s="15"/>
@@ -8028,11 +8275,11 @@
       <c r="G297" s="13"/>
       <c r="H297" s="13"/>
       <c r="I297" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J297" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K297" s="15"/>
@@ -8050,11 +8297,11 @@
       <c r="G298" s="13"/>
       <c r="H298" s="13"/>
       <c r="I298" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J298" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K298" s="15"/>
@@ -8072,11 +8319,11 @@
       <c r="G299" s="13"/>
       <c r="H299" s="13"/>
       <c r="I299" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J299" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K299" s="15"/>
@@ -8094,11 +8341,11 @@
       <c r="G300" s="13"/>
       <c r="H300" s="13"/>
       <c r="I300" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J300" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K300" s="15"/>
@@ -8116,11 +8363,11 @@
       <c r="G301" s="13"/>
       <c r="H301" s="13"/>
       <c r="I301" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J301" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K301" s="15"/>
@@ -8138,11 +8385,11 @@
       <c r="G302" s="13"/>
       <c r="H302" s="13"/>
       <c r="I302" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J302" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K302" s="15"/>
@@ -8160,11 +8407,11 @@
       <c r="G303" s="13"/>
       <c r="H303" s="13"/>
       <c r="I303" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J303" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K303" s="15"/>
@@ -8182,11 +8429,11 @@
       <c r="G304" s="13"/>
       <c r="H304" s="13"/>
       <c r="I304" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J304" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K304" s="15"/>
@@ -8204,11 +8451,11 @@
       <c r="G305" s="13"/>
       <c r="H305" s="13"/>
       <c r="I305" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J305" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K305" s="15"/>
@@ -8226,11 +8473,11 @@
       <c r="G306" s="13"/>
       <c r="H306" s="13"/>
       <c r="I306" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J306" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K306" s="15"/>
@@ -8248,11 +8495,11 @@
       <c r="G307" s="13"/>
       <c r="H307" s="13"/>
       <c r="I307" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J307" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K307" s="15"/>
@@ -8270,11 +8517,11 @@
       <c r="G308" s="13"/>
       <c r="H308" s="13"/>
       <c r="I308" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J308" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K308" s="15"/>
@@ -8292,11 +8539,11 @@
       <c r="G309" s="13"/>
       <c r="H309" s="13"/>
       <c r="I309" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J309" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K309" s="15"/>
@@ -8314,11 +8561,11 @@
       <c r="G310" s="13"/>
       <c r="H310" s="13"/>
       <c r="I310" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J310" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K310" s="15"/>
@@ -8336,11 +8583,11 @@
       <c r="G311" s="13"/>
       <c r="H311" s="13"/>
       <c r="I311" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J311" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K311" s="15"/>
@@ -8358,11 +8605,11 @@
       <c r="G312" s="13"/>
       <c r="H312" s="13"/>
       <c r="I312" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J312" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K312" s="15"/>
@@ -8380,11 +8627,11 @@
       <c r="G313" s="13"/>
       <c r="H313" s="13"/>
       <c r="I313" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J313" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K313" s="15"/>
@@ -8402,11 +8649,11 @@
       <c r="G314" s="13"/>
       <c r="H314" s="13"/>
       <c r="I314" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J314" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K314" s="15"/>
@@ -8424,11 +8671,11 @@
       <c r="G315" s="13"/>
       <c r="H315" s="13"/>
       <c r="I315" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J315" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K315" s="15"/>
@@ -8446,11 +8693,11 @@
       <c r="G316" s="13"/>
       <c r="H316" s="13"/>
       <c r="I316" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J316" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K316" s="15"/>
@@ -8468,11 +8715,11 @@
       <c r="G317" s="13"/>
       <c r="H317" s="13"/>
       <c r="I317" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J317" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K317" s="15"/>
@@ -8490,11 +8737,11 @@
       <c r="G318" s="13"/>
       <c r="H318" s="13"/>
       <c r="I318" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J318" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K318" s="15"/>
@@ -8512,11 +8759,11 @@
       <c r="G319" s="13"/>
       <c r="H319" s="13"/>
       <c r="I319" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J319" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K319" s="15"/>
@@ -8534,11 +8781,11 @@
       <c r="G320" s="13"/>
       <c r="H320" s="13"/>
       <c r="I320" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J320" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K320" s="15"/>
@@ -8556,11 +8803,11 @@
       <c r="G321" s="13"/>
       <c r="H321" s="13"/>
       <c r="I321" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J321" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K321" s="15"/>
@@ -8578,11 +8825,11 @@
       <c r="G322" s="13"/>
       <c r="H322" s="13"/>
       <c r="I322" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J322" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K322" s="15"/>
@@ -8600,11 +8847,11 @@
       <c r="G323" s="13"/>
       <c r="H323" s="13"/>
       <c r="I323" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J323" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K323" s="15"/>
@@ -8622,11 +8869,11 @@
       <c r="G324" s="13"/>
       <c r="H324" s="13"/>
       <c r="I324" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J324" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K324" s="15"/>
@@ -8644,11 +8891,11 @@
       <c r="G325" s="13"/>
       <c r="H325" s="13"/>
       <c r="I325" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J325" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K325" s="15"/>
@@ -8666,11 +8913,11 @@
       <c r="G326" s="13"/>
       <c r="H326" s="13"/>
       <c r="I326" s="14" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="12">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="14" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="13">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="15"/>
@@ -8688,11 +8935,11 @@
       <c r="G327" s="13"/>
       <c r="H327" s="13"/>
       <c r="I327" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J327" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K327" s="15"/>
@@ -8710,11 +8957,11 @@
       <c r="G328" s="13"/>
       <c r="H328" s="13"/>
       <c r="I328" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J328" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K328" s="15"/>
@@ -8732,11 +8979,11 @@
       <c r="G329" s="13"/>
       <c r="H329" s="13"/>
       <c r="I329" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J329" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K329" s="15"/>
@@ -8754,11 +9001,11 @@
       <c r="G330" s="13"/>
       <c r="H330" s="13"/>
       <c r="I330" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J330" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K330" s="15"/>
@@ -8776,11 +9023,11 @@
       <c r="G331" s="13"/>
       <c r="H331" s="13"/>
       <c r="I331" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J331" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K331" s="15"/>
@@ -8798,11 +9045,11 @@
       <c r="G332" s="13"/>
       <c r="H332" s="13"/>
       <c r="I332" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J332" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K332" s="15"/>
@@ -8820,11 +9067,11 @@
       <c r="G333" s="13"/>
       <c r="H333" s="13"/>
       <c r="I333" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J333" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K333" s="15"/>
@@ -8842,11 +9089,11 @@
       <c r="G334" s="13"/>
       <c r="H334" s="13"/>
       <c r="I334" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J334" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K334" s="15"/>
@@ -8864,11 +9111,11 @@
       <c r="G335" s="13"/>
       <c r="H335" s="13"/>
       <c r="I335" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J335" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K335" s="15"/>
@@ -8886,11 +9133,11 @@
       <c r="G336" s="13"/>
       <c r="H336" s="13"/>
       <c r="I336" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J336" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K336" s="15"/>
@@ -8908,11 +9155,11 @@
       <c r="G337" s="13"/>
       <c r="H337" s="13"/>
       <c r="I337" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J337" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K337" s="15"/>
@@ -8930,11 +9177,11 @@
       <c r="G338" s="13"/>
       <c r="H338" s="13"/>
       <c r="I338" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J338" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K338" s="15"/>
@@ -8952,11 +9199,11 @@
       <c r="G339" s="13"/>
       <c r="H339" s="13"/>
       <c r="I339" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J339" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K339" s="15"/>
@@ -8974,11 +9221,11 @@
       <c r="G340" s="13"/>
       <c r="H340" s="13"/>
       <c r="I340" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J340" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K340" s="15"/>
@@ -8996,11 +9243,11 @@
       <c r="G341" s="13"/>
       <c r="H341" s="13"/>
       <c r="I341" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J341" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K341" s="15"/>
@@ -9018,11 +9265,11 @@
       <c r="G342" s="13"/>
       <c r="H342" s="13"/>
       <c r="I342" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J342" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K342" s="15"/>
@@ -9040,11 +9287,11 @@
       <c r="G343" s="13"/>
       <c r="H343" s="13"/>
       <c r="I343" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J343" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K343" s="15"/>
@@ -9062,11 +9309,11 @@
       <c r="G344" s="13"/>
       <c r="H344" s="13"/>
       <c r="I344" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J344" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K344" s="15"/>
@@ -9084,11 +9331,11 @@
       <c r="G345" s="13"/>
       <c r="H345" s="13"/>
       <c r="I345" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J345" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K345" s="15"/>
@@ -9106,11 +9353,11 @@
       <c r="G346" s="13"/>
       <c r="H346" s="13"/>
       <c r="I346" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J346" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K346" s="15"/>
@@ -9128,11 +9375,11 @@
       <c r="G347" s="13"/>
       <c r="H347" s="13"/>
       <c r="I347" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J347" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K347" s="15"/>
@@ -9150,11 +9397,11 @@
       <c r="G348" s="13"/>
       <c r="H348" s="13"/>
       <c r="I348" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J348" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K348" s="15"/>
@@ -9172,11 +9419,11 @@
       <c r="G349" s="13"/>
       <c r="H349" s="13"/>
       <c r="I349" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J349" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K349" s="15"/>
@@ -9194,11 +9441,11 @@
       <c r="G350" s="13"/>
       <c r="H350" s="13"/>
       <c r="I350" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J350" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K350" s="15"/>
@@ -9216,11 +9463,11 @@
       <c r="G351" s="13"/>
       <c r="H351" s="13"/>
       <c r="I351" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J351" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K351" s="15"/>
@@ -9238,11 +9485,11 @@
       <c r="G352" s="13"/>
       <c r="H352" s="13"/>
       <c r="I352" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J352" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K352" s="15"/>
@@ -9260,11 +9507,11 @@
       <c r="G353" s="13"/>
       <c r="H353" s="13"/>
       <c r="I353" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J353" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K353" s="15"/>
@@ -9282,11 +9529,11 @@
       <c r="G354" s="13"/>
       <c r="H354" s="13"/>
       <c r="I354" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J354" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K354" s="15"/>
@@ -9304,11 +9551,11 @@
       <c r="G355" s="13"/>
       <c r="H355" s="13"/>
       <c r="I355" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J355" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K355" s="15"/>
@@ -9326,11 +9573,11 @@
       <c r="G356" s="13"/>
       <c r="H356" s="13"/>
       <c r="I356" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J356" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K356" s="15"/>
@@ -9348,11 +9595,11 @@
       <c r="G357" s="13"/>
       <c r="H357" s="13"/>
       <c r="I357" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J357" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K357" s="15"/>
@@ -9370,11 +9617,11 @@
       <c r="G358" s="13"/>
       <c r="H358" s="13"/>
       <c r="I358" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J358" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K358" s="15"/>
@@ -9392,11 +9639,11 @@
       <c r="G359" s="13"/>
       <c r="H359" s="13"/>
       <c r="I359" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J359" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K359" s="15"/>
@@ -9414,11 +9661,11 @@
       <c r="G360" s="13"/>
       <c r="H360" s="13"/>
       <c r="I360" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J360" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K360" s="15"/>
@@ -9436,11 +9683,11 @@
       <c r="G361" s="13"/>
       <c r="H361" s="13"/>
       <c r="I361" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J361" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K361" s="15"/>
@@ -9458,11 +9705,11 @@
       <c r="G362" s="13"/>
       <c r="H362" s="13"/>
       <c r="I362" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J362" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K362" s="15"/>
@@ -9480,11 +9727,11 @@
       <c r="G363" s="13"/>
       <c r="H363" s="13"/>
       <c r="I363" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J363" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K363" s="15"/>
@@ -9502,11 +9749,11 @@
       <c r="G364" s="13"/>
       <c r="H364" s="13"/>
       <c r="I364" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J364" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K364" s="15"/>
@@ -9524,11 +9771,11 @@
       <c r="G365" s="13"/>
       <c r="H365" s="13"/>
       <c r="I365" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J365" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K365" s="15"/>
@@ -9546,11 +9793,11 @@
       <c r="G366" s="13"/>
       <c r="H366" s="13"/>
       <c r="I366" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J366" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K366" s="15"/>
@@ -9568,11 +9815,11 @@
       <c r="G367" s="13"/>
       <c r="H367" s="13"/>
       <c r="I367" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J367" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K367" s="15"/>
@@ -9590,11 +9837,11 @@
       <c r="G368" s="13"/>
       <c r="H368" s="13"/>
       <c r="I368" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J368" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K368" s="15"/>
@@ -9612,11 +9859,11 @@
       <c r="G369" s="13"/>
       <c r="H369" s="13"/>
       <c r="I369" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J369" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K369" s="15"/>
@@ -9634,11 +9881,11 @@
       <c r="G370" s="13"/>
       <c r="H370" s="13"/>
       <c r="I370" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J370" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K370" s="15"/>
@@ -9656,11 +9903,11 @@
       <c r="G371" s="13"/>
       <c r="H371" s="13"/>
       <c r="I371" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J371" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K371" s="15"/>
@@ -9678,11 +9925,11 @@
       <c r="G372" s="13"/>
       <c r="H372" s="13"/>
       <c r="I372" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J372" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K372" s="15"/>
@@ -9700,11 +9947,11 @@
       <c r="G373" s="13"/>
       <c r="H373" s="13"/>
       <c r="I373" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J373" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K373" s="15"/>
@@ -9722,11 +9969,11 @@
       <c r="G374" s="13"/>
       <c r="H374" s="13"/>
       <c r="I374" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J374" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K374" s="15"/>
@@ -9744,11 +9991,11 @@
       <c r="G375" s="13"/>
       <c r="H375" s="13"/>
       <c r="I375" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J375" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K375" s="15"/>
@@ -9766,11 +10013,11 @@
       <c r="G376" s="13"/>
       <c r="H376" s="13"/>
       <c r="I376" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J376" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K376" s="15"/>
@@ -9788,11 +10035,11 @@
       <c r="G377" s="13"/>
       <c r="H377" s="13"/>
       <c r="I377" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J377" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K377" s="15"/>
@@ -9810,11 +10057,11 @@
       <c r="G378" s="13"/>
       <c r="H378" s="13"/>
       <c r="I378" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J378" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K378" s="15"/>
@@ -9832,11 +10079,11 @@
       <c r="G379" s="13"/>
       <c r="H379" s="13"/>
       <c r="I379" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J379" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K379" s="15"/>
@@ -9854,11 +10101,11 @@
       <c r="G380" s="13"/>
       <c r="H380" s="13"/>
       <c r="I380" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J380" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K380" s="15"/>
@@ -9876,11 +10123,11 @@
       <c r="G381" s="13"/>
       <c r="H381" s="13"/>
       <c r="I381" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J381" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K381" s="15"/>
@@ -9898,11 +10145,11 @@
       <c r="G382" s="13"/>
       <c r="H382" s="13"/>
       <c r="I382" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J382" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K382" s="15"/>
@@ -9920,11 +10167,11 @@
       <c r="G383" s="13"/>
       <c r="H383" s="13"/>
       <c r="I383" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J383" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K383" s="15"/>
@@ -9942,11 +10189,11 @@
       <c r="G384" s="13"/>
       <c r="H384" s="13"/>
       <c r="I384" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J384" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K384" s="15"/>
@@ -9964,11 +10211,11 @@
       <c r="G385" s="13"/>
       <c r="H385" s="13"/>
       <c r="I385" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J385" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K385" s="15"/>
@@ -9986,11 +10233,11 @@
       <c r="G386" s="13"/>
       <c r="H386" s="13"/>
       <c r="I386" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J386" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K386" s="15"/>
@@ -10008,11 +10255,11 @@
       <c r="G387" s="13"/>
       <c r="H387" s="13"/>
       <c r="I387" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J387" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K387" s="15"/>
@@ -10030,11 +10277,11 @@
       <c r="G388" s="13"/>
       <c r="H388" s="13"/>
       <c r="I388" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J388" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K388" s="15"/>
@@ -10052,11 +10299,11 @@
       <c r="G389" s="13"/>
       <c r="H389" s="13"/>
       <c r="I389" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J389" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K389" s="15"/>
@@ -10074,11 +10321,11 @@
       <c r="G390" s="13"/>
       <c r="H390" s="13"/>
       <c r="I390" s="14" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="14">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="14" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="15">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="15"/>
@@ -10096,11 +10343,11 @@
       <c r="G391" s="13"/>
       <c r="H391" s="13"/>
       <c r="I391" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J391" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K391" s="15"/>
@@ -10118,11 +10365,11 @@
       <c r="G392" s="13"/>
       <c r="H392" s="13"/>
       <c r="I392" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J392" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K392" s="15"/>
@@ -10140,11 +10387,11 @@
       <c r="G393" s="13"/>
       <c r="H393" s="13"/>
       <c r="I393" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J393" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K393" s="15"/>
@@ -10162,11 +10409,11 @@
       <c r="G394" s="13"/>
       <c r="H394" s="13"/>
       <c r="I394" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J394" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K394" s="15"/>
@@ -10184,11 +10431,11 @@
       <c r="G395" s="13"/>
       <c r="H395" s="13"/>
       <c r="I395" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J395" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K395" s="15"/>
@@ -10206,11 +10453,11 @@
       <c r="G396" s="13"/>
       <c r="H396" s="13"/>
       <c r="I396" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J396" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K396" s="15"/>
@@ -10228,11 +10475,11 @@
       <c r="G397" s="13"/>
       <c r="H397" s="13"/>
       <c r="I397" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J397" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K397" s="15"/>
@@ -10250,11 +10497,11 @@
       <c r="G398" s="13"/>
       <c r="H398" s="13"/>
       <c r="I398" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J398" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K398" s="15"/>
@@ -10272,11 +10519,11 @@
       <c r="G399" s="13"/>
       <c r="H399" s="13"/>
       <c r="I399" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J399" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K399" s="15"/>
@@ -10294,11 +10541,11 @@
       <c r="G400" s="13"/>
       <c r="H400" s="13"/>
       <c r="I400" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J400" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K400" s="15"/>
@@ -10316,11 +10563,11 @@
       <c r="G401" s="13"/>
       <c r="H401" s="13"/>
       <c r="I401" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J401" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K401" s="15"/>

--- a/12604714.xlsx
+++ b/12604714.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30509"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af964434807192f7/Documents/cap776^J12604714/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="403" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BEF87174-EA0A-422C-B666-48CEEC0C75C3}"/>
+  <xr:revisionPtr revIDLastSave="418" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEBAEBA1-A97E-41FA-9E1F-3904E56750F6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -283,6 +283,9 @@
   </si>
   <si>
     <t>today I have 8 class 4 lecture 4 pratical</t>
+  </si>
+  <si>
+    <t>today I have 4 class 2 lecture 2 pratical</t>
   </si>
 </sst>
 </file>
@@ -2223,7 +2226,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="15">
+    <row r="30" spans="1:14" ht="28.5">
       <c r="A30" s="8">
         <v>46269</v>
       </c>
@@ -2262,8 +2265,12 @@
       <c r="L30" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="M30" s="15"/>
-      <c r="N30" s="16"/>
+      <c r="M30" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N30" s="23" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="31" spans="1:14" ht="15">
       <c r="A31" s="8">
@@ -2541,29 +2548,51 @@
         <v>79</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="15">
+    <row r="37" spans="1:14" ht="28.5">
       <c r="A37" s="8">
         <v>46276</v>
       </c>
-      <c r="B37" s="13"/>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="13"/>
-      <c r="H37" s="13"/>
-      <c r="I37" s="14" t="str">
+      <c r="B37" s="13">
+        <v>320</v>
+      </c>
+      <c r="C37" s="13">
+        <v>50</v>
+      </c>
+      <c r="D37" s="13">
+        <v>60</v>
+      </c>
+      <c r="E37" s="13">
+        <v>50</v>
+      </c>
+      <c r="F37" s="13">
+        <v>200</v>
+      </c>
+      <c r="G37" s="13">
+        <v>4</v>
+      </c>
+      <c r="H37" s="13">
+        <v>120</v>
+      </c>
+      <c r="I37" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="14" t="str">
+        <v>800</v>
+      </c>
+      <c r="J37" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="15"/>
-      <c r="L37" s="15"/>
-      <c r="M37" s="15"/>
-      <c r="N37" s="16"/>
+        <v>640</v>
+      </c>
+      <c r="K37" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L37" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="M37" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N37" s="23" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="38" spans="1:14" ht="15">
       <c r="A38" s="8">

--- a/12604714.xlsx
+++ b/12604714.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30509"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af964434807192f7/Documents/cap776^J12604714/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="418" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AEBAEBA1-A97E-41FA-9E1F-3904E56750F6}"/>
+  <xr:revisionPtr revIDLastSave="488" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6EC88DE-6853-4CE4-9469-EC4284D987BB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -286,6 +286,9 @@
   </si>
   <si>
     <t>today I have 4 class 2 lecture 2 pratical</t>
+  </si>
+  <si>
+    <t>today I have 6 class 4 lecture 2 pratical</t>
   </si>
 </sst>
 </file>
@@ -2598,138 +2601,270 @@
       <c r="A38" s="8">
         <v>46277</v>
       </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="14" t="str">
+      <c r="B38" s="13">
+        <v>300</v>
+      </c>
+      <c r="C38" s="13">
+        <v>45</v>
+      </c>
+      <c r="D38" s="13">
+        <v>60</v>
+      </c>
+      <c r="E38" s="13">
+        <v>120</v>
+      </c>
+      <c r="F38" s="13">
+        <v>0</v>
+      </c>
+      <c r="G38" s="13">
+        <v>0</v>
+      </c>
+      <c r="H38" s="13">
+        <v>180</v>
+      </c>
+      <c r="I38" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="14" t="str">
+        <v>705</v>
+      </c>
+      <c r="J38" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="15"/>
-      <c r="L38" s="15"/>
-      <c r="M38" s="15"/>
-      <c r="N38" s="16"/>
-    </row>
-    <row r="39" spans="1:14">
-      <c r="A39" s="12"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
-      <c r="I39" s="14" t="str">
+        <v>735</v>
+      </c>
+      <c r="K38" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="L38" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M38" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N38" s="16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="15">
+      <c r="A39" s="8">
+        <v>46278</v>
+      </c>
+      <c r="B39" s="13">
+        <v>320</v>
+      </c>
+      <c r="C39" s="13">
+        <v>30</v>
+      </c>
+      <c r="D39" s="13">
+        <v>40</v>
+      </c>
+      <c r="E39" s="13">
+        <v>110</v>
+      </c>
+      <c r="F39" s="13">
+        <v>0</v>
+      </c>
+      <c r="G39" s="13">
+        <v>0</v>
+      </c>
+      <c r="H39" s="13">
+        <v>200</v>
+      </c>
+      <c r="I39" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="14" t="str">
+        <v>700</v>
+      </c>
+      <c r="J39" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="15"/>
-      <c r="L39" s="15"/>
-      <c r="M39" s="15"/>
-      <c r="N39" s="16"/>
-    </row>
-    <row r="40" spans="1:14">
-      <c r="A40" s="12"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="14" t="str">
+        <v>740</v>
+      </c>
+      <c r="K39" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L39" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M39" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="N39" s="16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="28.5">
+      <c r="A40" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B40" s="13">
+        <v>300</v>
+      </c>
+      <c r="C40" s="13">
+        <v>60</v>
+      </c>
+      <c r="D40" s="13">
+        <v>30</v>
+      </c>
+      <c r="E40" s="13">
+        <v>100</v>
+      </c>
+      <c r="F40" s="13">
+        <v>100</v>
+      </c>
+      <c r="G40" s="13">
+        <v>2</v>
+      </c>
+      <c r="H40" s="13">
+        <v>120</v>
+      </c>
+      <c r="I40" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="14" t="str">
+        <v>710</v>
+      </c>
+      <c r="J40" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="15"/>
-      <c r="L40" s="15"/>
-      <c r="M40" s="15"/>
-      <c r="N40" s="16"/>
-    </row>
-    <row r="41" spans="1:14">
-      <c r="A41" s="12"/>
-      <c r="B41" s="13"/>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="14" t="str">
+        <v>730</v>
+      </c>
+      <c r="K40" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L40" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M40" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="N40" s="23" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="28.5">
+      <c r="A41" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B41" s="13">
+        <v>320</v>
+      </c>
+      <c r="C41" s="13">
+        <v>45</v>
+      </c>
+      <c r="D41" s="13">
+        <v>60</v>
+      </c>
+      <c r="E41" s="13">
+        <v>45</v>
+      </c>
+      <c r="F41" s="13">
+        <v>300</v>
+      </c>
+      <c r="G41" s="13">
+        <v>6</v>
+      </c>
+      <c r="H41" s="13">
+        <v>160</v>
+      </c>
+      <c r="I41" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="14" t="str">
+        <v>930</v>
+      </c>
+      <c r="J41" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="15"/>
-      <c r="L41" s="15"/>
-      <c r="M41" s="15"/>
-      <c r="N41" s="16"/>
-    </row>
-    <row r="42" spans="1:14">
-      <c r="A42" s="12"/>
-      <c r="B42" s="13"/>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="14" t="str">
+        <v>510</v>
+      </c>
+      <c r="K41" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L41" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M41" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N41" s="23" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="28.5">
+      <c r="A42" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B42" s="13">
+        <v>300</v>
+      </c>
+      <c r="C42" s="13">
+        <v>50</v>
+      </c>
+      <c r="D42" s="13">
+        <v>45</v>
+      </c>
+      <c r="E42" s="13">
+        <v>45</v>
+      </c>
+      <c r="F42" s="13">
+        <v>400</v>
+      </c>
+      <c r="G42" s="13">
+        <v>8</v>
+      </c>
+      <c r="H42" s="13">
+        <v>120</v>
+      </c>
+      <c r="I42" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="14" t="str">
+        <v>960</v>
+      </c>
+      <c r="J42" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="15"/>
-      <c r="L42" s="15"/>
-      <c r="M42" s="15"/>
-      <c r="N42" s="16"/>
-    </row>
-    <row r="43" spans="1:14">
-      <c r="A43" s="12"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
+        <v>480</v>
+      </c>
+      <c r="K42" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L42" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M42" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N42" s="23" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="28.5">
+      <c r="A43" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B43" s="13">
+        <v>340</v>
+      </c>
+      <c r="C43" s="13">
+        <v>60</v>
+      </c>
+      <c r="D43" s="13">
+        <v>90</v>
+      </c>
+      <c r="E43" s="13">
+        <v>50</v>
+      </c>
       <c r="F43" s="13"/>
       <c r="G43" s="13"/>
       <c r="H43" s="13"/>
-      <c r="I43" s="14" t="str">
+      <c r="I43" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="14" t="str">
+        <v>540</v>
+      </c>
+      <c r="J43" s="14">
         <f t="shared" si="1"/>
-        <v/>
+        <v>900</v>
       </c>
       <c r="K43" s="15"/>
       <c r="L43" s="15"/>
       <c r="M43" s="15"/>
-      <c r="N43" s="16"/>
-    </row>
-    <row r="44" spans="1:14">
-      <c r="A44" s="12"/>
+      <c r="N43" s="23" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="15">
+      <c r="A44" s="8">
+        <v>46283</v>
+      </c>
       <c r="B44" s="13"/>
       <c r="C44" s="13"/>
       <c r="D44" s="13"/>
@@ -2750,8 +2885,10 @@
       <c r="M44" s="15"/>
       <c r="N44" s="16"/>
     </row>
-    <row r="45" spans="1:14">
-      <c r="A45" s="12"/>
+    <row r="45" spans="1:14" ht="15">
+      <c r="A45" s="8">
+        <v>46284</v>
+      </c>
       <c r="B45" s="13"/>
       <c r="C45" s="13"/>
       <c r="D45" s="13"/>

--- a/12604714.xlsx
+++ b/12604714.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af964434807192f7/Documents/cap776^J12604714/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="488" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B6EC88DE-6853-4CE4-9469-EC4284D987BB}"/>
+  <xr:revisionPtr revIDLastSave="502" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91E95697-9C79-4690-B8CD-375DC62C1977}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -289,6 +289,9 @@
   </si>
   <si>
     <t>today I have 6 class 4 lecture 2 pratical</t>
+  </si>
+  <si>
+    <t>today I have 8 class 5 lecture 3 pratical</t>
   </si>
 </sst>
 </file>
@@ -2824,42 +2827,26 @@
         <v>55</v>
       </c>
       <c r="N42" s="23" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14" ht="28.5">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="15">
       <c r="A43" s="8">
         <v>46282</v>
       </c>
-      <c r="B43" s="13">
-        <v>340</v>
-      </c>
-      <c r="C43" s="13">
-        <v>60</v>
-      </c>
-      <c r="D43" s="13">
-        <v>90</v>
-      </c>
-      <c r="E43" s="13">
-        <v>50</v>
-      </c>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
       <c r="F43" s="13"/>
       <c r="G43" s="13"/>
       <c r="H43" s="13"/>
-      <c r="I43" s="14">
-        <f t="shared" si="0"/>
-        <v>540</v>
-      </c>
-      <c r="J43" s="14">
-        <f t="shared" si="1"/>
-        <v>900</v>
-      </c>
+      <c r="I43" s="14"/>
+      <c r="J43" s="14"/>
       <c r="K43" s="15"/>
       <c r="L43" s="15"/>
       <c r="M43" s="15"/>
-      <c r="N43" s="23" t="s">
-        <v>81</v>
-      </c>
+      <c r="N43" s="23"/>
     </row>
     <row r="44" spans="1:14" ht="15">
       <c r="A44" s="8">

--- a/12604714.xlsx
+++ b/12604714.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30502"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af964434807192f7/Documents/cap776^J12604714/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="502" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91E95697-9C79-4690-B8CD-375DC62C1977}"/>
+  <xr:revisionPtr revIDLastSave="531" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC18A76E-7749-44F1-8BA4-56820B5370BA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2810,11 +2810,11 @@
         <v>120</v>
       </c>
       <c r="I42" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I42:I47" si="4">IF(SUM(B42:F42,H42)=0,"",SUM(B42:F42,H42))</f>
         <v>960</v>
       </c>
       <c r="J42" s="14">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J42:J47" si="5">IF(I42="","",1440-I42)</f>
         <v>480</v>
       </c>
       <c r="K42" s="15" t="s">
@@ -2830,47 +2830,97 @@
         <v>83</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="15">
+    <row r="43" spans="1:14" ht="28.5">
       <c r="A43" s="8">
         <v>46282</v>
       </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
-      <c r="G43" s="13"/>
-      <c r="H43" s="13"/>
-      <c r="I43" s="14"/>
-      <c r="J43" s="14"/>
-      <c r="K43" s="15"/>
-      <c r="L43" s="15"/>
-      <c r="M43" s="15"/>
-      <c r="N43" s="23"/>
-    </row>
-    <row r="44" spans="1:14" ht="15">
+      <c r="B43" s="13">
+        <v>320</v>
+      </c>
+      <c r="C43" s="13">
+        <v>45</v>
+      </c>
+      <c r="D43" s="13">
+        <v>60</v>
+      </c>
+      <c r="E43" s="13">
+        <v>45</v>
+      </c>
+      <c r="F43" s="13">
+        <v>250</v>
+      </c>
+      <c r="G43" s="13">
+        <v>5</v>
+      </c>
+      <c r="H43" s="13">
+        <v>180</v>
+      </c>
+      <c r="I43" s="14">
+        <f t="shared" si="4"/>
+        <v>900</v>
+      </c>
+      <c r="J43" s="14">
+        <f t="shared" si="5"/>
+        <v>540</v>
+      </c>
+      <c r="K43" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L43" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M43" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="N43" s="23" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="28.5">
       <c r="A44" s="8">
         <v>46283</v>
       </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
-      <c r="G44" s="13"/>
-      <c r="H44" s="13"/>
-      <c r="I44" s="14" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="14" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="15"/>
-      <c r="L44" s="15"/>
-      <c r="M44" s="15"/>
-      <c r="N44" s="16"/>
+      <c r="B44" s="13">
+        <v>300</v>
+      </c>
+      <c r="C44" s="13">
+        <v>50</v>
+      </c>
+      <c r="D44" s="13">
+        <v>80</v>
+      </c>
+      <c r="E44" s="13">
+        <v>60</v>
+      </c>
+      <c r="F44" s="13">
+        <v>300</v>
+      </c>
+      <c r="G44" s="13">
+        <v>6</v>
+      </c>
+      <c r="H44" s="13">
+        <v>120</v>
+      </c>
+      <c r="I44" s="14">
+        <f t="shared" si="4"/>
+        <v>910</v>
+      </c>
+      <c r="J44" s="14">
+        <f t="shared" si="5"/>
+        <v>530</v>
+      </c>
+      <c r="K44" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L44" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M44" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N44" s="23" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="45" spans="1:14" ht="15">
       <c r="A45" s="8">
@@ -2884,11 +2934,11 @@
       <c r="G45" s="13"/>
       <c r="H45" s="13"/>
       <c r="I45" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J45" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K45" s="15"/>
@@ -2896,7 +2946,7 @@
       <c r="M45" s="15"/>
       <c r="N45" s="16"/>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:14" ht="15">
       <c r="A46" s="12"/>
       <c r="B46" s="13"/>
       <c r="C46" s="13"/>
@@ -2906,11 +2956,11 @@
       <c r="G46" s="13"/>
       <c r="H46" s="13"/>
       <c r="I46" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J46" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K46" s="15"/>
@@ -2918,7 +2968,7 @@
       <c r="M46" s="15"/>
       <c r="N46" s="16"/>
     </row>
-    <row r="47" spans="1:14">
+    <row r="47" spans="1:14" ht="15">
       <c r="A47" s="12"/>
       <c r="B47" s="13"/>
       <c r="C47" s="13"/>
@@ -2928,11 +2978,11 @@
       <c r="G47" s="13"/>
       <c r="H47" s="13"/>
       <c r="I47" s="14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J47" s="14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K47" s="15"/>
@@ -3434,11 +3484,11 @@
       <c r="G70" s="13"/>
       <c r="H70" s="13"/>
       <c r="I70" s="14" t="str">
-        <f t="shared" ref="I70:I133" si="4">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" ref="I70:I133" si="6">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="14" t="str">
-        <f t="shared" ref="J70:J133" si="5">IF(I70="","",1440-I70)</f>
+        <f t="shared" ref="J70:J133" si="7">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="15"/>
@@ -3456,11 +3506,11 @@
       <c r="G71" s="13"/>
       <c r="H71" s="13"/>
       <c r="I71" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J71" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K71" s="15"/>
@@ -3478,11 +3528,11 @@
       <c r="G72" s="13"/>
       <c r="H72" s="13"/>
       <c r="I72" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J72" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K72" s="15"/>
@@ -3500,11 +3550,11 @@
       <c r="G73" s="13"/>
       <c r="H73" s="13"/>
       <c r="I73" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J73" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K73" s="15"/>
@@ -3522,11 +3572,11 @@
       <c r="G74" s="13"/>
       <c r="H74" s="13"/>
       <c r="I74" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J74" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K74" s="15"/>
@@ -3544,11 +3594,11 @@
       <c r="G75" s="13"/>
       <c r="H75" s="13"/>
       <c r="I75" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J75" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K75" s="15"/>
@@ -3566,11 +3616,11 @@
       <c r="G76" s="13"/>
       <c r="H76" s="13"/>
       <c r="I76" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J76" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K76" s="15"/>
@@ -3588,11 +3638,11 @@
       <c r="G77" s="13"/>
       <c r="H77" s="13"/>
       <c r="I77" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J77" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K77" s="15"/>
@@ -3610,11 +3660,11 @@
       <c r="G78" s="13"/>
       <c r="H78" s="13"/>
       <c r="I78" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J78" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K78" s="15"/>
@@ -3632,11 +3682,11 @@
       <c r="G79" s="13"/>
       <c r="H79" s="13"/>
       <c r="I79" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J79" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K79" s="15"/>
@@ -3654,11 +3704,11 @@
       <c r="G80" s="13"/>
       <c r="H80" s="13"/>
       <c r="I80" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J80" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K80" s="15"/>
@@ -3676,11 +3726,11 @@
       <c r="G81" s="13"/>
       <c r="H81" s="13"/>
       <c r="I81" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J81" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K81" s="15"/>
@@ -3698,11 +3748,11 @@
       <c r="G82" s="13"/>
       <c r="H82" s="13"/>
       <c r="I82" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J82" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K82" s="15"/>
@@ -3720,11 +3770,11 @@
       <c r="G83" s="13"/>
       <c r="H83" s="13"/>
       <c r="I83" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J83" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K83" s="15"/>
@@ -3742,11 +3792,11 @@
       <c r="G84" s="13"/>
       <c r="H84" s="13"/>
       <c r="I84" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J84" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K84" s="15"/>
@@ -3764,11 +3814,11 @@
       <c r="G85" s="13"/>
       <c r="H85" s="13"/>
       <c r="I85" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J85" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K85" s="15"/>
@@ -3786,11 +3836,11 @@
       <c r="G86" s="13"/>
       <c r="H86" s="13"/>
       <c r="I86" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J86" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K86" s="15"/>
@@ -3808,11 +3858,11 @@
       <c r="G87" s="13"/>
       <c r="H87" s="13"/>
       <c r="I87" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J87" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K87" s="15"/>
@@ -3830,11 +3880,11 @@
       <c r="G88" s="13"/>
       <c r="H88" s="13"/>
       <c r="I88" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J88" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K88" s="15"/>
@@ -3852,11 +3902,11 @@
       <c r="G89" s="13"/>
       <c r="H89" s="13"/>
       <c r="I89" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J89" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K89" s="15"/>
@@ -3874,11 +3924,11 @@
       <c r="G90" s="13"/>
       <c r="H90" s="13"/>
       <c r="I90" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J90" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K90" s="15"/>
@@ -3896,11 +3946,11 @@
       <c r="G91" s="13"/>
       <c r="H91" s="13"/>
       <c r="I91" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J91" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K91" s="15"/>
@@ -3918,11 +3968,11 @@
       <c r="G92" s="13"/>
       <c r="H92" s="13"/>
       <c r="I92" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J92" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K92" s="15"/>
@@ -3940,11 +3990,11 @@
       <c r="G93" s="13"/>
       <c r="H93" s="13"/>
       <c r="I93" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J93" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K93" s="15"/>
@@ -3962,11 +4012,11 @@
       <c r="G94" s="13"/>
       <c r="H94" s="13"/>
       <c r="I94" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J94" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K94" s="15"/>
@@ -3984,11 +4034,11 @@
       <c r="G95" s="13"/>
       <c r="H95" s="13"/>
       <c r="I95" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J95" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K95" s="15"/>
@@ -4006,11 +4056,11 @@
       <c r="G96" s="13"/>
       <c r="H96" s="13"/>
       <c r="I96" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J96" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K96" s="15"/>
@@ -4028,11 +4078,11 @@
       <c r="G97" s="13"/>
       <c r="H97" s="13"/>
       <c r="I97" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J97" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K97" s="15"/>
@@ -4050,11 +4100,11 @@
       <c r="G98" s="13"/>
       <c r="H98" s="13"/>
       <c r="I98" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J98" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K98" s="15"/>
@@ -4072,11 +4122,11 @@
       <c r="G99" s="13"/>
       <c r="H99" s="13"/>
       <c r="I99" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J99" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K99" s="15"/>
@@ -4094,11 +4144,11 @@
       <c r="G100" s="13"/>
       <c r="H100" s="13"/>
       <c r="I100" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J100" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K100" s="15"/>
@@ -4116,11 +4166,11 @@
       <c r="G101" s="13"/>
       <c r="H101" s="13"/>
       <c r="I101" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J101" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K101" s="15"/>
@@ -4138,11 +4188,11 @@
       <c r="G102" s="13"/>
       <c r="H102" s="13"/>
       <c r="I102" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J102" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K102" s="15"/>
@@ -4160,11 +4210,11 @@
       <c r="G103" s="13"/>
       <c r="H103" s="13"/>
       <c r="I103" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J103" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K103" s="15"/>
@@ -4182,11 +4232,11 @@
       <c r="G104" s="13"/>
       <c r="H104" s="13"/>
       <c r="I104" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J104" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K104" s="15"/>
@@ -4204,11 +4254,11 @@
       <c r="G105" s="13"/>
       <c r="H105" s="13"/>
       <c r="I105" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J105" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K105" s="15"/>
@@ -4226,11 +4276,11 @@
       <c r="G106" s="13"/>
       <c r="H106" s="13"/>
       <c r="I106" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J106" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K106" s="15"/>
@@ -4248,11 +4298,11 @@
       <c r="G107" s="13"/>
       <c r="H107" s="13"/>
       <c r="I107" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J107" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K107" s="15"/>
@@ -4270,11 +4320,11 @@
       <c r="G108" s="13"/>
       <c r="H108" s="13"/>
       <c r="I108" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J108" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K108" s="15"/>
@@ -4292,11 +4342,11 @@
       <c r="G109" s="13"/>
       <c r="H109" s="13"/>
       <c r="I109" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J109" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K109" s="15"/>
@@ -4314,11 +4364,11 @@
       <c r="G110" s="13"/>
       <c r="H110" s="13"/>
       <c r="I110" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J110" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K110" s="15"/>
@@ -4336,11 +4386,11 @@
       <c r="G111" s="13"/>
       <c r="H111" s="13"/>
       <c r="I111" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J111" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K111" s="15"/>
@@ -4358,11 +4408,11 @@
       <c r="G112" s="13"/>
       <c r="H112" s="13"/>
       <c r="I112" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J112" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K112" s="15"/>
@@ -4380,11 +4430,11 @@
       <c r="G113" s="13"/>
       <c r="H113" s="13"/>
       <c r="I113" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J113" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K113" s="15"/>
@@ -4402,11 +4452,11 @@
       <c r="G114" s="13"/>
       <c r="H114" s="13"/>
       <c r="I114" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J114" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K114" s="15"/>
@@ -4424,11 +4474,11 @@
       <c r="G115" s="13"/>
       <c r="H115" s="13"/>
       <c r="I115" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J115" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K115" s="15"/>
@@ -4446,11 +4496,11 @@
       <c r="G116" s="13"/>
       <c r="H116" s="13"/>
       <c r="I116" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J116" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K116" s="15"/>
@@ -4468,11 +4518,11 @@
       <c r="G117" s="13"/>
       <c r="H117" s="13"/>
       <c r="I117" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J117" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K117" s="15"/>
@@ -4490,11 +4540,11 @@
       <c r="G118" s="13"/>
       <c r="H118" s="13"/>
       <c r="I118" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J118" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K118" s="15"/>
@@ -4512,11 +4562,11 @@
       <c r="G119" s="13"/>
       <c r="H119" s="13"/>
       <c r="I119" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J119" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K119" s="15"/>
@@ -4534,11 +4584,11 @@
       <c r="G120" s="13"/>
       <c r="H120" s="13"/>
       <c r="I120" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J120" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K120" s="15"/>
@@ -4556,11 +4606,11 @@
       <c r="G121" s="13"/>
       <c r="H121" s="13"/>
       <c r="I121" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J121" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K121" s="15"/>
@@ -4578,11 +4628,11 @@
       <c r="G122" s="13"/>
       <c r="H122" s="13"/>
       <c r="I122" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J122" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K122" s="15"/>
@@ -4600,11 +4650,11 @@
       <c r="G123" s="13"/>
       <c r="H123" s="13"/>
       <c r="I123" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J123" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K123" s="15"/>
@@ -4622,11 +4672,11 @@
       <c r="G124" s="13"/>
       <c r="H124" s="13"/>
       <c r="I124" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J124" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K124" s="15"/>
@@ -4644,11 +4694,11 @@
       <c r="G125" s="13"/>
       <c r="H125" s="13"/>
       <c r="I125" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J125" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K125" s="15"/>
@@ -4666,11 +4716,11 @@
       <c r="G126" s="13"/>
       <c r="H126" s="13"/>
       <c r="I126" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J126" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K126" s="15"/>
@@ -4688,11 +4738,11 @@
       <c r="G127" s="13"/>
       <c r="H127" s="13"/>
       <c r="I127" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J127" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K127" s="15"/>
@@ -4710,11 +4760,11 @@
       <c r="G128" s="13"/>
       <c r="H128" s="13"/>
       <c r="I128" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J128" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K128" s="15"/>
@@ -4732,11 +4782,11 @@
       <c r="G129" s="13"/>
       <c r="H129" s="13"/>
       <c r="I129" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J129" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K129" s="15"/>
@@ -4754,11 +4804,11 @@
       <c r="G130" s="13"/>
       <c r="H130" s="13"/>
       <c r="I130" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J130" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K130" s="15"/>
@@ -4776,11 +4826,11 @@
       <c r="G131" s="13"/>
       <c r="H131" s="13"/>
       <c r="I131" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J131" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K131" s="15"/>
@@ -4798,11 +4848,11 @@
       <c r="G132" s="13"/>
       <c r="H132" s="13"/>
       <c r="I132" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J132" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K132" s="15"/>
@@ -4820,11 +4870,11 @@
       <c r="G133" s="13"/>
       <c r="H133" s="13"/>
       <c r="I133" s="14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J133" s="14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K133" s="15"/>
@@ -4842,11 +4892,11 @@
       <c r="G134" s="13"/>
       <c r="H134" s="13"/>
       <c r="I134" s="14" t="str">
-        <f t="shared" ref="I134:I197" si="6">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" ref="I134:I197" si="8">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="14" t="str">
-        <f t="shared" ref="J134:J197" si="7">IF(I134="","",1440-I134)</f>
+        <f t="shared" ref="J134:J197" si="9">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="15"/>
@@ -4864,11 +4914,11 @@
       <c r="G135" s="13"/>
       <c r="H135" s="13"/>
       <c r="I135" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J135" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K135" s="15"/>
@@ -4886,11 +4936,11 @@
       <c r="G136" s="13"/>
       <c r="H136" s="13"/>
       <c r="I136" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J136" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K136" s="15"/>
@@ -4908,11 +4958,11 @@
       <c r="G137" s="13"/>
       <c r="H137" s="13"/>
       <c r="I137" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J137" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K137" s="15"/>
@@ -4930,11 +4980,11 @@
       <c r="G138" s="13"/>
       <c r="H138" s="13"/>
       <c r="I138" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J138" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K138" s="15"/>
@@ -4952,11 +5002,11 @@
       <c r="G139" s="13"/>
       <c r="H139" s="13"/>
       <c r="I139" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J139" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K139" s="15"/>
@@ -4974,11 +5024,11 @@
       <c r="G140" s="13"/>
       <c r="H140" s="13"/>
       <c r="I140" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J140" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K140" s="15"/>
@@ -4996,11 +5046,11 @@
       <c r="G141" s="13"/>
       <c r="H141" s="13"/>
       <c r="I141" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J141" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K141" s="15"/>
@@ -5018,11 +5068,11 @@
       <c r="G142" s="13"/>
       <c r="H142" s="13"/>
       <c r="I142" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J142" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K142" s="15"/>
@@ -5040,11 +5090,11 @@
       <c r="G143" s="13"/>
       <c r="H143" s="13"/>
       <c r="I143" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J143" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K143" s="15"/>
@@ -5062,11 +5112,11 @@
       <c r="G144" s="13"/>
       <c r="H144" s="13"/>
       <c r="I144" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J144" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K144" s="15"/>
@@ -5084,11 +5134,11 @@
       <c r="G145" s="13"/>
       <c r="H145" s="13"/>
       <c r="I145" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J145" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K145" s="15"/>
@@ -5106,11 +5156,11 @@
       <c r="G146" s="13"/>
       <c r="H146" s="13"/>
       <c r="I146" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J146" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K146" s="15"/>
@@ -5128,11 +5178,11 @@
       <c r="G147" s="13"/>
       <c r="H147" s="13"/>
       <c r="I147" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J147" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K147" s="15"/>
@@ -5150,11 +5200,11 @@
       <c r="G148" s="13"/>
       <c r="H148" s="13"/>
       <c r="I148" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J148" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K148" s="15"/>
@@ -5172,11 +5222,11 @@
       <c r="G149" s="13"/>
       <c r="H149" s="13"/>
       <c r="I149" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J149" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K149" s="15"/>
@@ -5194,11 +5244,11 @@
       <c r="G150" s="13"/>
       <c r="H150" s="13"/>
       <c r="I150" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J150" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K150" s="15"/>
@@ -5216,11 +5266,11 @@
       <c r="G151" s="13"/>
       <c r="H151" s="13"/>
       <c r="I151" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J151" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K151" s="15"/>
@@ -5238,11 +5288,11 @@
       <c r="G152" s="13"/>
       <c r="H152" s="13"/>
       <c r="I152" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J152" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K152" s="15"/>
@@ -5260,11 +5310,11 @@
       <c r="G153" s="13"/>
       <c r="H153" s="13"/>
       <c r="I153" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J153" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K153" s="15"/>
@@ -5282,11 +5332,11 @@
       <c r="G154" s="13"/>
       <c r="H154" s="13"/>
       <c r="I154" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J154" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K154" s="15"/>
@@ -5304,11 +5354,11 @@
       <c r="G155" s="13"/>
       <c r="H155" s="13"/>
       <c r="I155" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J155" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K155" s="15"/>
@@ -5326,11 +5376,11 @@
       <c r="G156" s="13"/>
       <c r="H156" s="13"/>
       <c r="I156" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J156" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K156" s="15"/>
@@ -5348,11 +5398,11 @@
       <c r="G157" s="13"/>
       <c r="H157" s="13"/>
       <c r="I157" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J157" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K157" s="15"/>
@@ -5370,11 +5420,11 @@
       <c r="G158" s="13"/>
       <c r="H158" s="13"/>
       <c r="I158" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J158" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K158" s="15"/>
@@ -5392,11 +5442,11 @@
       <c r="G159" s="13"/>
       <c r="H159" s="13"/>
       <c r="I159" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J159" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K159" s="15"/>
@@ -5414,11 +5464,11 @@
       <c r="G160" s="13"/>
       <c r="H160" s="13"/>
       <c r="I160" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J160" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K160" s="15"/>
@@ -5436,11 +5486,11 @@
       <c r="G161" s="13"/>
       <c r="H161" s="13"/>
       <c r="I161" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J161" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K161" s="15"/>
@@ -5458,11 +5508,11 @@
       <c r="G162" s="13"/>
       <c r="H162" s="13"/>
       <c r="I162" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J162" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K162" s="15"/>
@@ -5480,11 +5530,11 @@
       <c r="G163" s="13"/>
       <c r="H163" s="13"/>
       <c r="I163" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J163" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K163" s="15"/>
@@ -5502,11 +5552,11 @@
       <c r="G164" s="13"/>
       <c r="H164" s="13"/>
       <c r="I164" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J164" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K164" s="15"/>
@@ -5524,11 +5574,11 @@
       <c r="G165" s="13"/>
       <c r="H165" s="13"/>
       <c r="I165" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J165" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K165" s="15"/>
@@ -5546,11 +5596,11 @@
       <c r="G166" s="13"/>
       <c r="H166" s="13"/>
       <c r="I166" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J166" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K166" s="15"/>
@@ -5568,11 +5618,11 @@
       <c r="G167" s="13"/>
       <c r="H167" s="13"/>
       <c r="I167" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J167" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K167" s="15"/>
@@ -5590,11 +5640,11 @@
       <c r="G168" s="13"/>
       <c r="H168" s="13"/>
       <c r="I168" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J168" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K168" s="15"/>
@@ -5612,11 +5662,11 @@
       <c r="G169" s="13"/>
       <c r="H169" s="13"/>
       <c r="I169" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J169" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K169" s="15"/>
@@ -5634,11 +5684,11 @@
       <c r="G170" s="13"/>
       <c r="H170" s="13"/>
       <c r="I170" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J170" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K170" s="15"/>
@@ -5656,11 +5706,11 @@
       <c r="G171" s="13"/>
       <c r="H171" s="13"/>
       <c r="I171" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J171" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K171" s="15"/>
@@ -5678,11 +5728,11 @@
       <c r="G172" s="13"/>
       <c r="H172" s="13"/>
       <c r="I172" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J172" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K172" s="15"/>
@@ -5700,11 +5750,11 @@
       <c r="G173" s="13"/>
       <c r="H173" s="13"/>
       <c r="I173" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J173" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K173" s="15"/>
@@ -5722,11 +5772,11 @@
       <c r="G174" s="13"/>
       <c r="H174" s="13"/>
       <c r="I174" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J174" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K174" s="15"/>
@@ -5744,11 +5794,11 @@
       <c r="G175" s="13"/>
       <c r="H175" s="13"/>
       <c r="I175" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J175" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K175" s="15"/>
@@ -5766,11 +5816,11 @@
       <c r="G176" s="13"/>
       <c r="H176" s="13"/>
       <c r="I176" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J176" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K176" s="15"/>
@@ -5788,11 +5838,11 @@
       <c r="G177" s="13"/>
       <c r="H177" s="13"/>
       <c r="I177" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J177" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K177" s="15"/>
@@ -5810,11 +5860,11 @@
       <c r="G178" s="13"/>
       <c r="H178" s="13"/>
       <c r="I178" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J178" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K178" s="15"/>
@@ -5832,11 +5882,11 @@
       <c r="G179" s="13"/>
       <c r="H179" s="13"/>
       <c r="I179" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J179" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K179" s="15"/>
@@ -5854,11 +5904,11 @@
       <c r="G180" s="13"/>
       <c r="H180" s="13"/>
       <c r="I180" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J180" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K180" s="15"/>
@@ -5876,11 +5926,11 @@
       <c r="G181" s="13"/>
       <c r="H181" s="13"/>
       <c r="I181" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J181" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K181" s="15"/>
@@ -5898,11 +5948,11 @@
       <c r="G182" s="13"/>
       <c r="H182" s="13"/>
       <c r="I182" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J182" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K182" s="15"/>
@@ -5920,11 +5970,11 @@
       <c r="G183" s="13"/>
       <c r="H183" s="13"/>
       <c r="I183" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J183" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K183" s="15"/>
@@ -5942,11 +5992,11 @@
       <c r="G184" s="13"/>
       <c r="H184" s="13"/>
       <c r="I184" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J184" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K184" s="15"/>
@@ -5964,11 +6014,11 @@
       <c r="G185" s="13"/>
       <c r="H185" s="13"/>
       <c r="I185" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J185" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K185" s="15"/>
@@ -5986,11 +6036,11 @@
       <c r="G186" s="13"/>
       <c r="H186" s="13"/>
       <c r="I186" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J186" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K186" s="15"/>
@@ -6008,11 +6058,11 @@
       <c r="G187" s="13"/>
       <c r="H187" s="13"/>
       <c r="I187" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J187" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K187" s="15"/>
@@ -6030,11 +6080,11 @@
       <c r="G188" s="13"/>
       <c r="H188" s="13"/>
       <c r="I188" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J188" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K188" s="15"/>
@@ -6052,11 +6102,11 @@
       <c r="G189" s="13"/>
       <c r="H189" s="13"/>
       <c r="I189" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J189" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K189" s="15"/>
@@ -6074,11 +6124,11 @@
       <c r="G190" s="13"/>
       <c r="H190" s="13"/>
       <c r="I190" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J190" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K190" s="15"/>
@@ -6096,11 +6146,11 @@
       <c r="G191" s="13"/>
       <c r="H191" s="13"/>
       <c r="I191" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J191" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K191" s="15"/>
@@ -6118,11 +6168,11 @@
       <c r="G192" s="13"/>
       <c r="H192" s="13"/>
       <c r="I192" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J192" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K192" s="15"/>
@@ -6140,11 +6190,11 @@
       <c r="G193" s="13"/>
       <c r="H193" s="13"/>
       <c r="I193" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J193" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K193" s="15"/>
@@ -6162,11 +6212,11 @@
       <c r="G194" s="13"/>
       <c r="H194" s="13"/>
       <c r="I194" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J194" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K194" s="15"/>
@@ -6184,11 +6234,11 @@
       <c r="G195" s="13"/>
       <c r="H195" s="13"/>
       <c r="I195" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J195" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K195" s="15"/>
@@ -6206,11 +6256,11 @@
       <c r="G196" s="13"/>
       <c r="H196" s="13"/>
       <c r="I196" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J196" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K196" s="15"/>
@@ -6228,11 +6278,11 @@
       <c r="G197" s="13"/>
       <c r="H197" s="13"/>
       <c r="I197" s="14" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J197" s="14" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K197" s="15"/>
@@ -6250,11 +6300,11 @@
       <c r="G198" s="13"/>
       <c r="H198" s="13"/>
       <c r="I198" s="14" t="str">
-        <f t="shared" ref="I198:I261" si="8">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" ref="I198:I261" si="10">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="14" t="str">
-        <f t="shared" ref="J198:J261" si="9">IF(I198="","",1440-I198)</f>
+        <f t="shared" ref="J198:J261" si="11">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="15"/>
@@ -6272,11 +6322,11 @@
       <c r="G199" s="13"/>
       <c r="H199" s="13"/>
       <c r="I199" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J199" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K199" s="15"/>
@@ -6294,11 +6344,11 @@
       <c r="G200" s="13"/>
       <c r="H200" s="13"/>
       <c r="I200" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J200" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K200" s="15"/>
@@ -6316,11 +6366,11 @@
       <c r="G201" s="13"/>
       <c r="H201" s="13"/>
       <c r="I201" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J201" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K201" s="15"/>
@@ -6338,11 +6388,11 @@
       <c r="G202" s="13"/>
       <c r="H202" s="13"/>
       <c r="I202" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J202" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K202" s="15"/>
@@ -6360,11 +6410,11 @@
       <c r="G203" s="13"/>
       <c r="H203" s="13"/>
       <c r="I203" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J203" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K203" s="15"/>
@@ -6382,11 +6432,11 @@
       <c r="G204" s="13"/>
       <c r="H204" s="13"/>
       <c r="I204" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J204" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K204" s="15"/>
@@ -6404,11 +6454,11 @@
       <c r="G205" s="13"/>
       <c r="H205" s="13"/>
       <c r="I205" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J205" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K205" s="15"/>
@@ -6426,11 +6476,11 @@
       <c r="G206" s="13"/>
       <c r="H206" s="13"/>
       <c r="I206" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J206" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K206" s="15"/>
@@ -6448,11 +6498,11 @@
       <c r="G207" s="13"/>
       <c r="H207" s="13"/>
       <c r="I207" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J207" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K207" s="15"/>
@@ -6470,11 +6520,11 @@
       <c r="G208" s="13"/>
       <c r="H208" s="13"/>
       <c r="I208" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J208" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K208" s="15"/>
@@ -6492,11 +6542,11 @@
       <c r="G209" s="13"/>
       <c r="H209" s="13"/>
       <c r="I209" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J209" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K209" s="15"/>
@@ -6514,11 +6564,11 @@
       <c r="G210" s="13"/>
       <c r="H210" s="13"/>
       <c r="I210" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J210" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K210" s="15"/>
@@ -6536,11 +6586,11 @@
       <c r="G211" s="13"/>
       <c r="H211" s="13"/>
       <c r="I211" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J211" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K211" s="15"/>
@@ -6558,11 +6608,11 @@
       <c r="G212" s="13"/>
       <c r="H212" s="13"/>
       <c r="I212" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J212" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K212" s="15"/>
@@ -6580,11 +6630,11 @@
       <c r="G213" s="13"/>
       <c r="H213" s="13"/>
       <c r="I213" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J213" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K213" s="15"/>
@@ -6602,11 +6652,11 @@
       <c r="G214" s="13"/>
       <c r="H214" s="13"/>
       <c r="I214" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J214" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K214" s="15"/>
@@ -6624,11 +6674,11 @@
       <c r="G215" s="13"/>
       <c r="H215" s="13"/>
       <c r="I215" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J215" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K215" s="15"/>
@@ -6646,11 +6696,11 @@
       <c r="G216" s="13"/>
       <c r="H216" s="13"/>
       <c r="I216" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J216" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K216" s="15"/>
@@ -6668,11 +6718,11 @@
       <c r="G217" s="13"/>
       <c r="H217" s="13"/>
       <c r="I217" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J217" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K217" s="15"/>
@@ -6690,11 +6740,11 @@
       <c r="G218" s="13"/>
       <c r="H218" s="13"/>
       <c r="I218" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J218" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K218" s="15"/>
@@ -6712,11 +6762,11 @@
       <c r="G219" s="13"/>
       <c r="H219" s="13"/>
       <c r="I219" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J219" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K219" s="15"/>
@@ -6734,11 +6784,11 @@
       <c r="G220" s="13"/>
       <c r="H220" s="13"/>
       <c r="I220" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J220" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K220" s="15"/>
@@ -6756,11 +6806,11 @@
       <c r="G221" s="13"/>
       <c r="H221" s="13"/>
       <c r="I221" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J221" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K221" s="15"/>
@@ -6778,11 +6828,11 @@
       <c r="G222" s="13"/>
       <c r="H222" s="13"/>
       <c r="I222" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J222" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K222" s="15"/>
@@ -6800,11 +6850,11 @@
       <c r="G223" s="13"/>
       <c r="H223" s="13"/>
       <c r="I223" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J223" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K223" s="15"/>
@@ -6822,11 +6872,11 @@
       <c r="G224" s="13"/>
       <c r="H224" s="13"/>
       <c r="I224" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J224" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K224" s="15"/>
@@ -6844,11 +6894,11 @@
       <c r="G225" s="13"/>
       <c r="H225" s="13"/>
       <c r="I225" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J225" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K225" s="15"/>
@@ -6866,11 +6916,11 @@
       <c r="G226" s="13"/>
       <c r="H226" s="13"/>
       <c r="I226" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J226" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K226" s="15"/>
@@ -6888,11 +6938,11 @@
       <c r="G227" s="13"/>
       <c r="H227" s="13"/>
       <c r="I227" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J227" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K227" s="15"/>
@@ -6910,11 +6960,11 @@
       <c r="G228" s="13"/>
       <c r="H228" s="13"/>
       <c r="I228" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J228" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K228" s="15"/>
@@ -6932,11 +6982,11 @@
       <c r="G229" s="13"/>
       <c r="H229" s="13"/>
       <c r="I229" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J229" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K229" s="15"/>
@@ -6954,11 +7004,11 @@
       <c r="G230" s="13"/>
       <c r="H230" s="13"/>
       <c r="I230" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J230" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K230" s="15"/>
@@ -6976,11 +7026,11 @@
       <c r="G231" s="13"/>
       <c r="H231" s="13"/>
       <c r="I231" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J231" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K231" s="15"/>
@@ -6998,11 +7048,11 @@
       <c r="G232" s="13"/>
       <c r="H232" s="13"/>
       <c r="I232" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J232" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K232" s="15"/>
@@ -7020,11 +7070,11 @@
       <c r="G233" s="13"/>
       <c r="H233" s="13"/>
       <c r="I233" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J233" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K233" s="15"/>
@@ -7042,11 +7092,11 @@
       <c r="G234" s="13"/>
       <c r="H234" s="13"/>
       <c r="I234" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J234" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K234" s="15"/>
@@ -7064,11 +7114,11 @@
       <c r="G235" s="13"/>
       <c r="H235" s="13"/>
       <c r="I235" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J235" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K235" s="15"/>
@@ -7086,11 +7136,11 @@
       <c r="G236" s="13"/>
       <c r="H236" s="13"/>
       <c r="I236" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J236" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K236" s="15"/>
@@ -7108,11 +7158,11 @@
       <c r="G237" s="13"/>
       <c r="H237" s="13"/>
       <c r="I237" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J237" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K237" s="15"/>
@@ -7130,11 +7180,11 @@
       <c r="G238" s="13"/>
       <c r="H238" s="13"/>
       <c r="I238" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J238" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K238" s="15"/>
@@ -7152,11 +7202,11 @@
       <c r="G239" s="13"/>
       <c r="H239" s="13"/>
       <c r="I239" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J239" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K239" s="15"/>
@@ -7174,11 +7224,11 @@
       <c r="G240" s="13"/>
       <c r="H240" s="13"/>
       <c r="I240" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J240" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K240" s="15"/>
@@ -7196,11 +7246,11 @@
       <c r="G241" s="13"/>
       <c r="H241" s="13"/>
       <c r="I241" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J241" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K241" s="15"/>
@@ -7218,11 +7268,11 @@
       <c r="G242" s="13"/>
       <c r="H242" s="13"/>
       <c r="I242" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J242" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K242" s="15"/>
@@ -7240,11 +7290,11 @@
       <c r="G243" s="13"/>
       <c r="H243" s="13"/>
       <c r="I243" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J243" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K243" s="15"/>
@@ -7262,11 +7312,11 @@
       <c r="G244" s="13"/>
       <c r="H244" s="13"/>
       <c r="I244" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J244" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K244" s="15"/>
@@ -7284,11 +7334,11 @@
       <c r="G245" s="13"/>
       <c r="H245" s="13"/>
       <c r="I245" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J245" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K245" s="15"/>
@@ -7306,11 +7356,11 @@
       <c r="G246" s="13"/>
       <c r="H246" s="13"/>
       <c r="I246" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J246" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K246" s="15"/>
@@ -7328,11 +7378,11 @@
       <c r="G247" s="13"/>
       <c r="H247" s="13"/>
       <c r="I247" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J247" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K247" s="15"/>
@@ -7350,11 +7400,11 @@
       <c r="G248" s="13"/>
       <c r="H248" s="13"/>
       <c r="I248" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J248" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K248" s="15"/>
@@ -7372,11 +7422,11 @@
       <c r="G249" s="13"/>
       <c r="H249" s="13"/>
       <c r="I249" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J249" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K249" s="15"/>
@@ -7394,11 +7444,11 @@
       <c r="G250" s="13"/>
       <c r="H250" s="13"/>
       <c r="I250" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J250" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K250" s="15"/>
@@ -7416,11 +7466,11 @@
       <c r="G251" s="13"/>
       <c r="H251" s="13"/>
       <c r="I251" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J251" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K251" s="15"/>
@@ -7438,11 +7488,11 @@
       <c r="G252" s="13"/>
       <c r="H252" s="13"/>
       <c r="I252" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J252" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K252" s="15"/>
@@ -7460,11 +7510,11 @@
       <c r="G253" s="13"/>
       <c r="H253" s="13"/>
       <c r="I253" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J253" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K253" s="15"/>
@@ -7482,11 +7532,11 @@
       <c r="G254" s="13"/>
       <c r="H254" s="13"/>
       <c r="I254" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J254" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K254" s="15"/>
@@ -7504,11 +7554,11 @@
       <c r="G255" s="13"/>
       <c r="H255" s="13"/>
       <c r="I255" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J255" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K255" s="15"/>
@@ -7526,11 +7576,11 @@
       <c r="G256" s="13"/>
       <c r="H256" s="13"/>
       <c r="I256" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J256" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K256" s="15"/>
@@ -7548,11 +7598,11 @@
       <c r="G257" s="13"/>
       <c r="H257" s="13"/>
       <c r="I257" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J257" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K257" s="15"/>
@@ -7570,11 +7620,11 @@
       <c r="G258" s="13"/>
       <c r="H258" s="13"/>
       <c r="I258" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J258" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K258" s="15"/>
@@ -7592,11 +7642,11 @@
       <c r="G259" s="13"/>
       <c r="H259" s="13"/>
       <c r="I259" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J259" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K259" s="15"/>
@@ -7614,11 +7664,11 @@
       <c r="G260" s="13"/>
       <c r="H260" s="13"/>
       <c r="I260" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J260" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K260" s="15"/>
@@ -7636,11 +7686,11 @@
       <c r="G261" s="13"/>
       <c r="H261" s="13"/>
       <c r="I261" s="14" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J261" s="14" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K261" s="15"/>
@@ -7658,11 +7708,11 @@
       <c r="G262" s="13"/>
       <c r="H262" s="13"/>
       <c r="I262" s="14" t="str">
-        <f t="shared" ref="I262:I325" si="10">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" ref="I262:I325" si="12">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="14" t="str">
-        <f t="shared" ref="J262:J325" si="11">IF(I262="","",1440-I262)</f>
+        <f t="shared" ref="J262:J325" si="13">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="15"/>
@@ -7680,11 +7730,11 @@
       <c r="G263" s="13"/>
       <c r="H263" s="13"/>
       <c r="I263" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J263" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K263" s="15"/>
@@ -7702,11 +7752,11 @@
       <c r="G264" s="13"/>
       <c r="H264" s="13"/>
       <c r="I264" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J264" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K264" s="15"/>
@@ -7724,11 +7774,11 @@
       <c r="G265" s="13"/>
       <c r="H265" s="13"/>
       <c r="I265" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J265" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K265" s="15"/>
@@ -7746,11 +7796,11 @@
       <c r="G266" s="13"/>
       <c r="H266" s="13"/>
       <c r="I266" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J266" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K266" s="15"/>
@@ -7768,11 +7818,11 @@
       <c r="G267" s="13"/>
       <c r="H267" s="13"/>
       <c r="I267" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J267" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K267" s="15"/>
@@ -7790,11 +7840,11 @@
       <c r="G268" s="13"/>
       <c r="H268" s="13"/>
       <c r="I268" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J268" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K268" s="15"/>
@@ -7812,11 +7862,11 @@
       <c r="G269" s="13"/>
       <c r="H269" s="13"/>
       <c r="I269" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J269" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K269" s="15"/>
@@ -7834,11 +7884,11 @@
       <c r="G270" s="13"/>
       <c r="H270" s="13"/>
       <c r="I270" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J270" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K270" s="15"/>
@@ -7856,11 +7906,11 @@
       <c r="G271" s="13"/>
       <c r="H271" s="13"/>
       <c r="I271" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J271" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K271" s="15"/>
@@ -7878,11 +7928,11 @@
       <c r="G272" s="13"/>
       <c r="H272" s="13"/>
       <c r="I272" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J272" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K272" s="15"/>
@@ -7900,11 +7950,11 @@
       <c r="G273" s="13"/>
       <c r="H273" s="13"/>
       <c r="I273" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J273" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K273" s="15"/>
@@ -7922,11 +7972,11 @@
       <c r="G274" s="13"/>
       <c r="H274" s="13"/>
       <c r="I274" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J274" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K274" s="15"/>
@@ -7944,11 +7994,11 @@
       <c r="G275" s="13"/>
       <c r="H275" s="13"/>
       <c r="I275" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J275" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K275" s="15"/>
@@ -7966,11 +8016,11 @@
       <c r="G276" s="13"/>
       <c r="H276" s="13"/>
       <c r="I276" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J276" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K276" s="15"/>
@@ -7988,11 +8038,11 @@
       <c r="G277" s="13"/>
       <c r="H277" s="13"/>
       <c r="I277" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J277" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K277" s="15"/>
@@ -8010,11 +8060,11 @@
       <c r="G278" s="13"/>
       <c r="H278" s="13"/>
       <c r="I278" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J278" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K278" s="15"/>
@@ -8032,11 +8082,11 @@
       <c r="G279" s="13"/>
       <c r="H279" s="13"/>
       <c r="I279" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J279" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K279" s="15"/>
@@ -8054,11 +8104,11 @@
       <c r="G280" s="13"/>
       <c r="H280" s="13"/>
       <c r="I280" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J280" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K280" s="15"/>
@@ -8076,11 +8126,11 @@
       <c r="G281" s="13"/>
       <c r="H281" s="13"/>
       <c r="I281" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J281" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K281" s="15"/>
@@ -8098,11 +8148,11 @@
       <c r="G282" s="13"/>
       <c r="H282" s="13"/>
       <c r="I282" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J282" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K282" s="15"/>
@@ -8120,11 +8170,11 @@
       <c r="G283" s="13"/>
       <c r="H283" s="13"/>
       <c r="I283" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J283" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K283" s="15"/>
@@ -8142,11 +8192,11 @@
       <c r="G284" s="13"/>
       <c r="H284" s="13"/>
       <c r="I284" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J284" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K284" s="15"/>
@@ -8164,11 +8214,11 @@
       <c r="G285" s="13"/>
       <c r="H285" s="13"/>
       <c r="I285" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J285" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K285" s="15"/>
@@ -8186,11 +8236,11 @@
       <c r="G286" s="13"/>
       <c r="H286" s="13"/>
       <c r="I286" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J286" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K286" s="15"/>
@@ -8208,11 +8258,11 @@
       <c r="G287" s="13"/>
       <c r="H287" s="13"/>
       <c r="I287" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J287" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K287" s="15"/>
@@ -8230,11 +8280,11 @@
       <c r="G288" s="13"/>
       <c r="H288" s="13"/>
       <c r="I288" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J288" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K288" s="15"/>
@@ -8252,11 +8302,11 @@
       <c r="G289" s="13"/>
       <c r="H289" s="13"/>
       <c r="I289" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J289" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K289" s="15"/>
@@ -8274,11 +8324,11 @@
       <c r="G290" s="13"/>
       <c r="H290" s="13"/>
       <c r="I290" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J290" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K290" s="15"/>
@@ -8296,11 +8346,11 @@
       <c r="G291" s="13"/>
       <c r="H291" s="13"/>
       <c r="I291" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J291" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K291" s="15"/>
@@ -8318,11 +8368,11 @@
       <c r="G292" s="13"/>
       <c r="H292" s="13"/>
       <c r="I292" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J292" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K292" s="15"/>
@@ -8340,11 +8390,11 @@
       <c r="G293" s="13"/>
       <c r="H293" s="13"/>
       <c r="I293" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J293" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K293" s="15"/>
@@ -8362,11 +8412,11 @@
       <c r="G294" s="13"/>
       <c r="H294" s="13"/>
       <c r="I294" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J294" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K294" s="15"/>
@@ -8384,11 +8434,11 @@
       <c r="G295" s="13"/>
       <c r="H295" s="13"/>
       <c r="I295" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J295" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K295" s="15"/>
@@ -8406,11 +8456,11 @@
       <c r="G296" s="13"/>
       <c r="H296" s="13"/>
       <c r="I296" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J296" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K296" s="15"/>
@@ -8428,11 +8478,11 @@
       <c r="G297" s="13"/>
       <c r="H297" s="13"/>
       <c r="I297" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J297" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K297" s="15"/>
@@ -8450,11 +8500,11 @@
       <c r="G298" s="13"/>
       <c r="H298" s="13"/>
       <c r="I298" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J298" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K298" s="15"/>
@@ -8472,11 +8522,11 @@
       <c r="G299" s="13"/>
       <c r="H299" s="13"/>
       <c r="I299" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J299" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K299" s="15"/>
@@ -8494,11 +8544,11 @@
       <c r="G300" s="13"/>
       <c r="H300" s="13"/>
       <c r="I300" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J300" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K300" s="15"/>
@@ -8516,11 +8566,11 @@
       <c r="G301" s="13"/>
       <c r="H301" s="13"/>
       <c r="I301" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J301" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K301" s="15"/>
@@ -8538,11 +8588,11 @@
       <c r="G302" s="13"/>
       <c r="H302" s="13"/>
       <c r="I302" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J302" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K302" s="15"/>
@@ -8560,11 +8610,11 @@
       <c r="G303" s="13"/>
       <c r="H303" s="13"/>
       <c r="I303" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J303" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K303" s="15"/>
@@ -8582,11 +8632,11 @@
       <c r="G304" s="13"/>
       <c r="H304" s="13"/>
       <c r="I304" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J304" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K304" s="15"/>
@@ -8604,11 +8654,11 @@
       <c r="G305" s="13"/>
       <c r="H305" s="13"/>
       <c r="I305" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J305" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K305" s="15"/>
@@ -8626,11 +8676,11 @@
       <c r="G306" s="13"/>
       <c r="H306" s="13"/>
       <c r="I306" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J306" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K306" s="15"/>
@@ -8648,11 +8698,11 @@
       <c r="G307" s="13"/>
       <c r="H307" s="13"/>
       <c r="I307" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J307" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K307" s="15"/>
@@ -8670,11 +8720,11 @@
       <c r="G308" s="13"/>
       <c r="H308" s="13"/>
       <c r="I308" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J308" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K308" s="15"/>
@@ -8692,11 +8742,11 @@
       <c r="G309" s="13"/>
       <c r="H309" s="13"/>
       <c r="I309" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J309" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K309" s="15"/>
@@ -8714,11 +8764,11 @@
       <c r="G310" s="13"/>
       <c r="H310" s="13"/>
       <c r="I310" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J310" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K310" s="15"/>
@@ -8736,11 +8786,11 @@
       <c r="G311" s="13"/>
       <c r="H311" s="13"/>
       <c r="I311" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J311" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K311" s="15"/>
@@ -8758,11 +8808,11 @@
       <c r="G312" s="13"/>
       <c r="H312" s="13"/>
       <c r="I312" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J312" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K312" s="15"/>
@@ -8780,11 +8830,11 @@
       <c r="G313" s="13"/>
       <c r="H313" s="13"/>
       <c r="I313" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J313" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K313" s="15"/>
@@ -8802,11 +8852,11 @@
       <c r="G314" s="13"/>
       <c r="H314" s="13"/>
       <c r="I314" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J314" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K314" s="15"/>
@@ -8824,11 +8874,11 @@
       <c r="G315" s="13"/>
       <c r="H315" s="13"/>
       <c r="I315" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J315" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K315" s="15"/>
@@ -8846,11 +8896,11 @@
       <c r="G316" s="13"/>
       <c r="H316" s="13"/>
       <c r="I316" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J316" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K316" s="15"/>
@@ -8868,11 +8918,11 @@
       <c r="G317" s="13"/>
       <c r="H317" s="13"/>
       <c r="I317" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J317" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K317" s="15"/>
@@ -8890,11 +8940,11 @@
       <c r="G318" s="13"/>
       <c r="H318" s="13"/>
       <c r="I318" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J318" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K318" s="15"/>
@@ -8912,11 +8962,11 @@
       <c r="G319" s="13"/>
       <c r="H319" s="13"/>
       <c r="I319" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J319" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K319" s="15"/>
@@ -8934,11 +8984,11 @@
       <c r="G320" s="13"/>
       <c r="H320" s="13"/>
       <c r="I320" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J320" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K320" s="15"/>
@@ -8956,11 +9006,11 @@
       <c r="G321" s="13"/>
       <c r="H321" s="13"/>
       <c r="I321" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J321" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K321" s="15"/>
@@ -8978,11 +9028,11 @@
       <c r="G322" s="13"/>
       <c r="H322" s="13"/>
       <c r="I322" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J322" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K322" s="15"/>
@@ -9000,11 +9050,11 @@
       <c r="G323" s="13"/>
       <c r="H323" s="13"/>
       <c r="I323" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J323" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K323" s="15"/>
@@ -9022,11 +9072,11 @@
       <c r="G324" s="13"/>
       <c r="H324" s="13"/>
       <c r="I324" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J324" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K324" s="15"/>
@@ -9044,11 +9094,11 @@
       <c r="G325" s="13"/>
       <c r="H325" s="13"/>
       <c r="I325" s="14" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J325" s="14" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K325" s="15"/>
@@ -9066,11 +9116,11 @@
       <c r="G326" s="13"/>
       <c r="H326" s="13"/>
       <c r="I326" s="14" t="str">
-        <f t="shared" ref="I326:I389" si="12">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" ref="I326:I389" si="14">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="14" t="str">
-        <f t="shared" ref="J326:J389" si="13">IF(I326="","",1440-I326)</f>
+        <f t="shared" ref="J326:J389" si="15">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="15"/>
@@ -9088,11 +9138,11 @@
       <c r="G327" s="13"/>
       <c r="H327" s="13"/>
       <c r="I327" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J327" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K327" s="15"/>
@@ -9110,11 +9160,11 @@
       <c r="G328" s="13"/>
       <c r="H328" s="13"/>
       <c r="I328" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J328" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K328" s="15"/>
@@ -9132,11 +9182,11 @@
       <c r="G329" s="13"/>
       <c r="H329" s="13"/>
       <c r="I329" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J329" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K329" s="15"/>
@@ -9154,11 +9204,11 @@
       <c r="G330" s="13"/>
       <c r="H330" s="13"/>
       <c r="I330" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J330" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K330" s="15"/>
@@ -9176,11 +9226,11 @@
       <c r="G331" s="13"/>
       <c r="H331" s="13"/>
       <c r="I331" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J331" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K331" s="15"/>
@@ -9198,11 +9248,11 @@
       <c r="G332" s="13"/>
       <c r="H332" s="13"/>
       <c r="I332" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J332" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K332" s="15"/>
@@ -9220,11 +9270,11 @@
       <c r="G333" s="13"/>
       <c r="H333" s="13"/>
       <c r="I333" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J333" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K333" s="15"/>
@@ -9242,11 +9292,11 @@
       <c r="G334" s="13"/>
       <c r="H334" s="13"/>
       <c r="I334" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J334" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K334" s="15"/>
@@ -9264,11 +9314,11 @@
       <c r="G335" s="13"/>
       <c r="H335" s="13"/>
       <c r="I335" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J335" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K335" s="15"/>
@@ -9286,11 +9336,11 @@
       <c r="G336" s="13"/>
       <c r="H336" s="13"/>
       <c r="I336" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J336" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K336" s="15"/>
@@ -9308,11 +9358,11 @@
       <c r="G337" s="13"/>
       <c r="H337" s="13"/>
       <c r="I337" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J337" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K337" s="15"/>
@@ -9330,11 +9380,11 @@
       <c r="G338" s="13"/>
       <c r="H338" s="13"/>
       <c r="I338" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J338" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K338" s="15"/>
@@ -9352,11 +9402,11 @@
       <c r="G339" s="13"/>
       <c r="H339" s="13"/>
       <c r="I339" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J339" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K339" s="15"/>
@@ -9374,11 +9424,11 @@
       <c r="G340" s="13"/>
       <c r="H340" s="13"/>
       <c r="I340" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J340" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K340" s="15"/>
@@ -9396,11 +9446,11 @@
       <c r="G341" s="13"/>
       <c r="H341" s="13"/>
       <c r="I341" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J341" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K341" s="15"/>
@@ -9418,11 +9468,11 @@
       <c r="G342" s="13"/>
       <c r="H342" s="13"/>
       <c r="I342" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J342" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K342" s="15"/>
@@ -9440,11 +9490,11 @@
       <c r="G343" s="13"/>
       <c r="H343" s="13"/>
       <c r="I343" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J343" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K343" s="15"/>
@@ -9462,11 +9512,11 @@
       <c r="G344" s="13"/>
       <c r="H344" s="13"/>
       <c r="I344" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J344" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K344" s="15"/>
@@ -9484,11 +9534,11 @@
       <c r="G345" s="13"/>
       <c r="H345" s="13"/>
       <c r="I345" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J345" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K345" s="15"/>
@@ -9506,11 +9556,11 @@
       <c r="G346" s="13"/>
       <c r="H346" s="13"/>
       <c r="I346" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J346" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K346" s="15"/>
@@ -9528,11 +9578,11 @@
       <c r="G347" s="13"/>
       <c r="H347" s="13"/>
       <c r="I347" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J347" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K347" s="15"/>
@@ -9550,11 +9600,11 @@
       <c r="G348" s="13"/>
       <c r="H348" s="13"/>
       <c r="I348" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J348" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K348" s="15"/>
@@ -9572,11 +9622,11 @@
       <c r="G349" s="13"/>
       <c r="H349" s="13"/>
       <c r="I349" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J349" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K349" s="15"/>
@@ -9594,11 +9644,11 @@
       <c r="G350" s="13"/>
       <c r="H350" s="13"/>
       <c r="I350" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J350" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K350" s="15"/>
@@ -9616,11 +9666,11 @@
       <c r="G351" s="13"/>
       <c r="H351" s="13"/>
       <c r="I351" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J351" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K351" s="15"/>
@@ -9638,11 +9688,11 @@
       <c r="G352" s="13"/>
       <c r="H352" s="13"/>
       <c r="I352" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J352" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K352" s="15"/>
@@ -9660,11 +9710,11 @@
       <c r="G353" s="13"/>
       <c r="H353" s="13"/>
       <c r="I353" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J353" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K353" s="15"/>
@@ -9682,11 +9732,11 @@
       <c r="G354" s="13"/>
       <c r="H354" s="13"/>
       <c r="I354" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J354" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K354" s="15"/>
@@ -9704,11 +9754,11 @@
       <c r="G355" s="13"/>
       <c r="H355" s="13"/>
       <c r="I355" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J355" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K355" s="15"/>
@@ -9726,11 +9776,11 @@
       <c r="G356" s="13"/>
       <c r="H356" s="13"/>
       <c r="I356" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J356" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K356" s="15"/>
@@ -9748,11 +9798,11 @@
       <c r="G357" s="13"/>
       <c r="H357" s="13"/>
       <c r="I357" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J357" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K357" s="15"/>
@@ -9770,11 +9820,11 @@
       <c r="G358" s="13"/>
       <c r="H358" s="13"/>
       <c r="I358" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J358" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K358" s="15"/>
@@ -9792,11 +9842,11 @@
       <c r="G359" s="13"/>
       <c r="H359" s="13"/>
       <c r="I359" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J359" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K359" s="15"/>
@@ -9814,11 +9864,11 @@
       <c r="G360" s="13"/>
       <c r="H360" s="13"/>
       <c r="I360" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J360" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K360" s="15"/>
@@ -9836,11 +9886,11 @@
       <c r="G361" s="13"/>
       <c r="H361" s="13"/>
       <c r="I361" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J361" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K361" s="15"/>
@@ -9858,11 +9908,11 @@
       <c r="G362" s="13"/>
       <c r="H362" s="13"/>
       <c r="I362" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J362" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K362" s="15"/>
@@ -9880,11 +9930,11 @@
       <c r="G363" s="13"/>
       <c r="H363" s="13"/>
       <c r="I363" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J363" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K363" s="15"/>
@@ -9902,11 +9952,11 @@
       <c r="G364" s="13"/>
       <c r="H364" s="13"/>
       <c r="I364" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J364" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K364" s="15"/>
@@ -9924,11 +9974,11 @@
       <c r="G365" s="13"/>
       <c r="H365" s="13"/>
       <c r="I365" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J365" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K365" s="15"/>
@@ -9946,11 +9996,11 @@
       <c r="G366" s="13"/>
       <c r="H366" s="13"/>
       <c r="I366" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J366" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K366" s="15"/>
@@ -9968,11 +10018,11 @@
       <c r="G367" s="13"/>
       <c r="H367" s="13"/>
       <c r="I367" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J367" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K367" s="15"/>
@@ -9990,11 +10040,11 @@
       <c r="G368" s="13"/>
       <c r="H368" s="13"/>
       <c r="I368" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J368" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K368" s="15"/>
@@ -10012,11 +10062,11 @@
       <c r="G369" s="13"/>
       <c r="H369" s="13"/>
       <c r="I369" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J369" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K369" s="15"/>
@@ -10034,11 +10084,11 @@
       <c r="G370" s="13"/>
       <c r="H370" s="13"/>
       <c r="I370" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J370" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K370" s="15"/>
@@ -10056,11 +10106,11 @@
       <c r="G371" s="13"/>
       <c r="H371" s="13"/>
       <c r="I371" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J371" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K371" s="15"/>
@@ -10078,11 +10128,11 @@
       <c r="G372" s="13"/>
       <c r="H372" s="13"/>
       <c r="I372" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J372" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K372" s="15"/>
@@ -10100,11 +10150,11 @@
       <c r="G373" s="13"/>
       <c r="H373" s="13"/>
       <c r="I373" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J373" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K373" s="15"/>
@@ -10122,11 +10172,11 @@
       <c r="G374" s="13"/>
       <c r="H374" s="13"/>
       <c r="I374" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J374" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K374" s="15"/>
@@ -10144,11 +10194,11 @@
       <c r="G375" s="13"/>
       <c r="H375" s="13"/>
       <c r="I375" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J375" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K375" s="15"/>
@@ -10166,11 +10216,11 @@
       <c r="G376" s="13"/>
       <c r="H376" s="13"/>
       <c r="I376" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J376" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K376" s="15"/>
@@ -10188,11 +10238,11 @@
       <c r="G377" s="13"/>
       <c r="H377" s="13"/>
       <c r="I377" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J377" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K377" s="15"/>
@@ -10210,11 +10260,11 @@
       <c r="G378" s="13"/>
       <c r="H378" s="13"/>
       <c r="I378" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J378" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K378" s="15"/>
@@ -10232,11 +10282,11 @@
       <c r="G379" s="13"/>
       <c r="H379" s="13"/>
       <c r="I379" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J379" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K379" s="15"/>
@@ -10254,11 +10304,11 @@
       <c r="G380" s="13"/>
       <c r="H380" s="13"/>
       <c r="I380" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J380" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K380" s="15"/>
@@ -10276,11 +10326,11 @@
       <c r="G381" s="13"/>
       <c r="H381" s="13"/>
       <c r="I381" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J381" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K381" s="15"/>
@@ -10298,11 +10348,11 @@
       <c r="G382" s="13"/>
       <c r="H382" s="13"/>
       <c r="I382" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J382" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K382" s="15"/>
@@ -10320,11 +10370,11 @@
       <c r="G383" s="13"/>
       <c r="H383" s="13"/>
       <c r="I383" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J383" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K383" s="15"/>
@@ -10342,11 +10392,11 @@
       <c r="G384" s="13"/>
       <c r="H384" s="13"/>
       <c r="I384" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J384" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K384" s="15"/>
@@ -10364,11 +10414,11 @@
       <c r="G385" s="13"/>
       <c r="H385" s="13"/>
       <c r="I385" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J385" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K385" s="15"/>
@@ -10386,11 +10436,11 @@
       <c r="G386" s="13"/>
       <c r="H386" s="13"/>
       <c r="I386" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J386" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K386" s="15"/>
@@ -10408,11 +10458,11 @@
       <c r="G387" s="13"/>
       <c r="H387" s="13"/>
       <c r="I387" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J387" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K387" s="15"/>
@@ -10430,11 +10480,11 @@
       <c r="G388" s="13"/>
       <c r="H388" s="13"/>
       <c r="I388" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J388" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K388" s="15"/>
@@ -10452,11 +10502,11 @@
       <c r="G389" s="13"/>
       <c r="H389" s="13"/>
       <c r="I389" s="14" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J389" s="14" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K389" s="15"/>
@@ -10474,11 +10524,11 @@
       <c r="G390" s="13"/>
       <c r="H390" s="13"/>
       <c r="I390" s="14" t="str">
-        <f t="shared" ref="I390:I401" si="14">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" ref="I390:I401" si="16">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="14" t="str">
-        <f t="shared" ref="J390:J401" si="15">IF(I390="","",1440-I390)</f>
+        <f t="shared" ref="J390:J401" si="17">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="15"/>
@@ -10496,11 +10546,11 @@
       <c r="G391" s="13"/>
       <c r="H391" s="13"/>
       <c r="I391" s="14" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J391" s="14" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K391" s="15"/>
@@ -10518,11 +10568,11 @@
       <c r="G392" s="13"/>
       <c r="H392" s="13"/>
       <c r="I392" s="14" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J392" s="14" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K392" s="15"/>
@@ -10540,11 +10590,11 @@
       <c r="G393" s="13"/>
       <c r="H393" s="13"/>
       <c r="I393" s="14" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J393" s="14" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K393" s="15"/>
@@ -10562,11 +10612,11 @@
       <c r="G394" s="13"/>
       <c r="H394" s="13"/>
       <c r="I394" s="14" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J394" s="14" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K394" s="15"/>
@@ -10584,11 +10634,11 @@
       <c r="G395" s="13"/>
       <c r="H395" s="13"/>
       <c r="I395" s="14" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J395" s="14" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K395" s="15"/>
@@ -10606,11 +10656,11 @@
       <c r="G396" s="13"/>
       <c r="H396" s="13"/>
       <c r="I396" s="14" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J396" s="14" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K396" s="15"/>
@@ -10628,11 +10678,11 @@
       <c r="G397" s="13"/>
       <c r="H397" s="13"/>
       <c r="I397" s="14" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J397" s="14" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K397" s="15"/>
@@ -10650,11 +10700,11 @@
       <c r="G398" s="13"/>
       <c r="H398" s="13"/>
       <c r="I398" s="14" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J398" s="14" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K398" s="15"/>
@@ -10672,11 +10722,11 @@
       <c r="G399" s="13"/>
       <c r="H399" s="13"/>
       <c r="I399" s="14" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J399" s="14" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K399" s="15"/>
@@ -10694,11 +10744,11 @@
       <c r="G400" s="13"/>
       <c r="H400" s="13"/>
       <c r="I400" s="14" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J400" s="14" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K400" s="15"/>
@@ -10716,11 +10766,11 @@
       <c r="G401" s="13"/>
       <c r="H401" s="13"/>
       <c r="I401" s="14" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="J401" s="14" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="K401" s="15"/>

--- a/12604714.xlsx
+++ b/12604714.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af964434807192f7/Documents/cap776^J12604714/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="531" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EC18A76E-7749-44F1-8BA4-56820B5370BA}"/>
+  <xr:revisionPtr revIDLastSave="540" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12F966A2-ABEF-4BCF-B875-AD0351C1E8BF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2926,22 +2926,38 @@
       <c r="A45" s="8">
         <v>46284</v>
       </c>
-      <c r="B45" s="13"/>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
-      <c r="G45" s="13"/>
-      <c r="H45" s="13"/>
-      <c r="I45" s="14" t="str">
+      <c r="B45" s="13">
+        <v>300</v>
+      </c>
+      <c r="C45" s="13">
+        <v>60</v>
+      </c>
+      <c r="D45" s="13">
+        <v>120</v>
+      </c>
+      <c r="E45" s="13">
+        <v>60</v>
+      </c>
+      <c r="F45" s="13">
+        <v>60</v>
+      </c>
+      <c r="G45" s="13">
+        <v>1</v>
+      </c>
+      <c r="H45" s="13">
+        <v>120</v>
+      </c>
+      <c r="I45" s="14">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J45" s="14" t="str">
+        <v>720</v>
+      </c>
+      <c r="J45" s="14">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K45" s="15"/>
+        <v>720</v>
+      </c>
+      <c r="K45" s="15" t="s">
+        <v>53</v>
+      </c>
       <c r="L45" s="15"/>
       <c r="M45" s="15"/>
       <c r="N45" s="16"/>

--- a/12604714.xlsx
+++ b/12604714.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af964434807192f7/Documents/cap776^J12604714/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="540" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12F966A2-ABEF-4BCF-B875-AD0351C1E8BF}"/>
+  <xr:revisionPtr revIDLastSave="558" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7C442CD-6432-47D5-B867-E26782151666}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -292,6 +292,9 @@
   </si>
   <si>
     <t>today I have 8 class 5 lecture 3 pratical</t>
+  </si>
+  <si>
+    <t>PAE CA</t>
   </si>
 </sst>
 </file>
@@ -2956,36 +2959,68 @@
         <v>720</v>
       </c>
       <c r="K45" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="L45" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M45" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="N45" s="16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="15">
+      <c r="A46" s="8">
+        <v>46285</v>
+      </c>
+      <c r="B46" s="13">
+        <v>320</v>
+      </c>
+      <c r="C46" s="13">
+        <v>50</v>
+      </c>
+      <c r="D46" s="13">
+        <v>120</v>
+      </c>
+      <c r="E46" s="13">
+        <v>45</v>
+      </c>
+      <c r="F46" s="13">
+        <v>0</v>
+      </c>
+      <c r="G46" s="13">
+        <v>0</v>
+      </c>
+      <c r="H46" s="13">
+        <v>320</v>
+      </c>
+      <c r="I46" s="14">
+        <f t="shared" si="4"/>
+        <v>855</v>
+      </c>
+      <c r="J46" s="14">
+        <f t="shared" si="5"/>
+        <v>585</v>
+      </c>
+      <c r="K46" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="L45" s="15"/>
-      <c r="M45" s="15"/>
-      <c r="N45" s="16"/>
-    </row>
-    <row r="46" spans="1:14" ht="15">
-      <c r="A46" s="12"/>
-      <c r="B46" s="13"/>
-      <c r="C46" s="13"/>
-      <c r="D46" s="13"/>
-      <c r="E46" s="13"/>
-      <c r="F46" s="13"/>
-      <c r="G46" s="13"/>
-      <c r="H46" s="13"/>
-      <c r="I46" s="14" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J46" s="14" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K46" s="15"/>
-      <c r="L46" s="15"/>
-      <c r="M46" s="15"/>
-      <c r="N46" s="16"/>
+      <c r="L46" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M46" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N46" s="16" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="47" spans="1:14" ht="15">
-      <c r="A47" s="12"/>
+      <c r="A47" s="8">
+        <v>46286</v>
+      </c>
       <c r="B47" s="13"/>
       <c r="C47" s="13"/>
       <c r="D47" s="13"/>
@@ -3006,8 +3041,10 @@
       <c r="M47" s="15"/>
       <c r="N47" s="16"/>
     </row>
-    <row r="48" spans="1:14">
-      <c r="A48" s="12"/>
+    <row r="48" spans="1:14" ht="15">
+      <c r="A48" s="8">
+        <v>46287</v>
+      </c>
       <c r="B48" s="13"/>
       <c r="C48" s="13"/>
       <c r="D48" s="13"/>
@@ -3028,8 +3065,10 @@
       <c r="M48" s="15"/>
       <c r="N48" s="16"/>
     </row>
-    <row r="49" spans="1:14">
-      <c r="A49" s="12"/>
+    <row r="49" spans="1:14" ht="15">
+      <c r="A49" s="8">
+        <v>46288</v>
+      </c>
       <c r="B49" s="13"/>
       <c r="C49" s="13"/>
       <c r="D49" s="13"/>
@@ -3050,8 +3089,10 @@
       <c r="M49" s="15"/>
       <c r="N49" s="16"/>
     </row>
-    <row r="50" spans="1:14">
-      <c r="A50" s="12"/>
+    <row r="50" spans="1:14" ht="15">
+      <c r="A50" s="8">
+        <v>46289</v>
+      </c>
       <c r="B50" s="13"/>
       <c r="C50" s="13"/>
       <c r="D50" s="13"/>
@@ -3072,8 +3113,10 @@
       <c r="M50" s="15"/>
       <c r="N50" s="16"/>
     </row>
-    <row r="51" spans="1:14">
-      <c r="A51" s="12"/>
+    <row r="51" spans="1:14" ht="15">
+      <c r="A51" s="8">
+        <v>46290</v>
+      </c>
       <c r="B51" s="13"/>
       <c r="C51" s="13"/>
       <c r="D51" s="13"/>
@@ -3094,8 +3137,10 @@
       <c r="M51" s="15"/>
       <c r="N51" s="16"/>
     </row>
-    <row r="52" spans="1:14">
-      <c r="A52" s="12"/>
+    <row r="52" spans="1:14" ht="15">
+      <c r="A52" s="8">
+        <v>46291</v>
+      </c>
       <c r="B52" s="13"/>
       <c r="C52" s="13"/>
       <c r="D52" s="13"/>
@@ -3116,8 +3161,10 @@
       <c r="M52" s="15"/>
       <c r="N52" s="16"/>
     </row>
-    <row r="53" spans="1:14">
-      <c r="A53" s="12"/>
+    <row r="53" spans="1:14" ht="15">
+      <c r="A53" s="8">
+        <v>46292</v>
+      </c>
       <c r="B53" s="13"/>
       <c r="C53" s="13"/>
       <c r="D53" s="13"/>
@@ -3138,8 +3185,10 @@
       <c r="M53" s="15"/>
       <c r="N53" s="16"/>
     </row>
-    <row r="54" spans="1:14">
-      <c r="A54" s="12"/>
+    <row r="54" spans="1:14" ht="15">
+      <c r="A54" s="8">
+        <v>46293</v>
+      </c>
       <c r="B54" s="13"/>
       <c r="C54" s="13"/>
       <c r="D54" s="13"/>
@@ -3160,8 +3209,10 @@
       <c r="M54" s="15"/>
       <c r="N54" s="16"/>
     </row>
-    <row r="55" spans="1:14">
-      <c r="A55" s="12"/>
+    <row r="55" spans="1:14" ht="15">
+      <c r="A55" s="8">
+        <v>46294</v>
+      </c>
       <c r="B55" s="13"/>
       <c r="C55" s="13"/>
       <c r="D55" s="13"/>
@@ -3182,8 +3233,10 @@
       <c r="M55" s="15"/>
       <c r="N55" s="16"/>
     </row>
-    <row r="56" spans="1:14">
-      <c r="A56" s="12"/>
+    <row r="56" spans="1:14" ht="15">
+      <c r="A56" s="8">
+        <v>46295</v>
+      </c>
       <c r="B56" s="13"/>
       <c r="C56" s="13"/>
       <c r="D56" s="13"/>
@@ -3204,8 +3257,10 @@
       <c r="M56" s="15"/>
       <c r="N56" s="16"/>
     </row>
-    <row r="57" spans="1:14">
-      <c r="A57" s="12"/>
+    <row r="57" spans="1:14" ht="15">
+      <c r="A57" s="8">
+        <v>46296</v>
+      </c>
       <c r="B57" s="13"/>
       <c r="C57" s="13"/>
       <c r="D57" s="13"/>
@@ -3226,8 +3281,10 @@
       <c r="M57" s="15"/>
       <c r="N57" s="16"/>
     </row>
-    <row r="58" spans="1:14">
-      <c r="A58" s="12"/>
+    <row r="58" spans="1:14" ht="15">
+      <c r="A58" s="8">
+        <v>46297</v>
+      </c>
       <c r="B58" s="13"/>
       <c r="C58" s="13"/>
       <c r="D58" s="13"/>
@@ -3248,8 +3305,10 @@
       <c r="M58" s="15"/>
       <c r="N58" s="16"/>
     </row>
-    <row r="59" spans="1:14">
-      <c r="A59" s="12"/>
+    <row r="59" spans="1:14" ht="15">
+      <c r="A59" s="8">
+        <v>46298</v>
+      </c>
       <c r="B59" s="13"/>
       <c r="C59" s="13"/>
       <c r="D59" s="13"/>
@@ -3270,8 +3329,10 @@
       <c r="M59" s="15"/>
       <c r="N59" s="16"/>
     </row>
-    <row r="60" spans="1:14">
-      <c r="A60" s="12"/>
+    <row r="60" spans="1:14" ht="15">
+      <c r="A60" s="8">
+        <v>46299</v>
+      </c>
       <c r="B60" s="13"/>
       <c r="C60" s="13"/>
       <c r="D60" s="13"/>
@@ -3292,8 +3353,10 @@
       <c r="M60" s="15"/>
       <c r="N60" s="16"/>
     </row>
-    <row r="61" spans="1:14">
-      <c r="A61" s="12"/>
+    <row r="61" spans="1:14" ht="15">
+      <c r="A61" s="8">
+        <v>46300</v>
+      </c>
       <c r="B61" s="13"/>
       <c r="C61" s="13"/>
       <c r="D61" s="13"/>
@@ -3314,8 +3377,10 @@
       <c r="M61" s="15"/>
       <c r="N61" s="16"/>
     </row>
-    <row r="62" spans="1:14">
-      <c r="A62" s="12"/>
+    <row r="62" spans="1:14" ht="15">
+      <c r="A62" s="8">
+        <v>46301</v>
+      </c>
       <c r="B62" s="13"/>
       <c r="C62" s="13"/>
       <c r="D62" s="13"/>
@@ -3336,8 +3401,10 @@
       <c r="M62" s="15"/>
       <c r="N62" s="16"/>
     </row>
-    <row r="63" spans="1:14">
-      <c r="A63" s="12"/>
+    <row r="63" spans="1:14" ht="15">
+      <c r="A63" s="8">
+        <v>46302</v>
+      </c>
       <c r="B63" s="13"/>
       <c r="C63" s="13"/>
       <c r="D63" s="13"/>
@@ -3358,8 +3425,10 @@
       <c r="M63" s="15"/>
       <c r="N63" s="16"/>
     </row>
-    <row r="64" spans="1:14">
-      <c r="A64" s="12"/>
+    <row r="64" spans="1:14" ht="15">
+      <c r="A64" s="8">
+        <v>46303</v>
+      </c>
       <c r="B64" s="13"/>
       <c r="C64" s="13"/>
       <c r="D64" s="13"/>
@@ -3380,8 +3449,10 @@
       <c r="M64" s="15"/>
       <c r="N64" s="16"/>
     </row>
-    <row r="65" spans="1:14">
-      <c r="A65" s="12"/>
+    <row r="65" spans="1:14" ht="15">
+      <c r="A65" s="8">
+        <v>46304</v>
+      </c>
       <c r="B65" s="13"/>
       <c r="C65" s="13"/>
       <c r="D65" s="13"/>
@@ -3402,8 +3473,10 @@
       <c r="M65" s="15"/>
       <c r="N65" s="16"/>
     </row>
-    <row r="66" spans="1:14">
-      <c r="A66" s="12"/>
+    <row r="66" spans="1:14" ht="15">
+      <c r="A66" s="8">
+        <v>46305</v>
+      </c>
       <c r="B66" s="13"/>
       <c r="C66" s="13"/>
       <c r="D66" s="13"/>

--- a/12604714.xlsx
+++ b/12604714.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30520"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af964434807192f7/Documents/cap776^J12604714/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="558" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E7C442CD-6432-47D5-B867-E26782151666}"/>
+  <xr:revisionPtr revIDLastSave="568" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A68D4A9-422D-46CE-81EB-B3D6693CE870}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3021,24 +3021,44 @@
       <c r="A47" s="8">
         <v>46286</v>
       </c>
-      <c r="B47" s="13"/>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
-      <c r="G47" s="13"/>
-      <c r="H47" s="13"/>
-      <c r="I47" s="14" t="str">
+      <c r="B47" s="13">
+        <v>330</v>
+      </c>
+      <c r="C47" s="13">
+        <v>40</v>
+      </c>
+      <c r="D47" s="13">
+        <v>150</v>
+      </c>
+      <c r="E47" s="13">
+        <v>60</v>
+      </c>
+      <c r="F47" s="13">
+        <v>100</v>
+      </c>
+      <c r="G47" s="13">
+        <v>2</v>
+      </c>
+      <c r="H47" s="13">
+        <v>240</v>
+      </c>
+      <c r="I47" s="14">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="J47" s="14" t="str">
+        <v>920</v>
+      </c>
+      <c r="J47" s="14">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="K47" s="15"/>
-      <c r="L47" s="15"/>
-      <c r="M47" s="15"/>
+        <v>520</v>
+      </c>
+      <c r="K47" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L47" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M47" s="15" t="s">
+        <v>58</v>
+      </c>
       <c r="N47" s="16"/>
     </row>
     <row r="48" spans="1:14" ht="15">

--- a/12604714.xlsx
+++ b/12604714.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30520"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af964434807192f7/Documents/cap776^J12604714/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="568" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A68D4A9-422D-46CE-81EB-B3D6693CE870}"/>
+  <xr:revisionPtr revIDLastSave="577" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF306906-3076-4A05-A41C-56E54640D4DA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3059,26 +3059,42 @@
       <c r="M47" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="N47" s="16"/>
+      <c r="N47" s="16" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="48" spans="1:14" ht="15">
       <c r="A48" s="8">
         <v>46287</v>
       </c>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-      <c r="H48" s="13"/>
-      <c r="I48" s="14" t="str">
+      <c r="B48" s="13">
+        <v>330</v>
+      </c>
+      <c r="C48" s="13">
+        <v>45</v>
+      </c>
+      <c r="D48" s="13">
+        <v>120</v>
+      </c>
+      <c r="E48" s="13">
+        <v>45</v>
+      </c>
+      <c r="F48" s="13">
+        <v>300</v>
+      </c>
+      <c r="G48" s="13">
+        <v>6</v>
+      </c>
+      <c r="H48" s="13">
+        <v>180</v>
+      </c>
+      <c r="I48" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="14" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J48" s="14">
         <f t="shared" si="1"/>
-        <v/>
+        <v>420</v>
       </c>
       <c r="K48" s="15"/>
       <c r="L48" s="15"/>

--- a/12604714.xlsx
+++ b/12604714.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af964434807192f7/Documents/cap776^J12604714/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="577" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF306906-3076-4A05-A41C-56E54640D4DA}"/>
+  <xr:revisionPtr revIDLastSave="583" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA4A5898-D4D3-4945-A5CB-35F1DE5993B0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t>PAE CA</t>
+  </si>
+  <si>
+    <t>today I have 6 class 2 lecture 4 pratical</t>
   </si>
 </sst>
 </file>
@@ -3063,7 +3066,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="15">
+    <row r="48" spans="1:14" ht="28.5">
       <c r="A48" s="8">
         <v>46287</v>
       </c>
@@ -3086,20 +3089,28 @@
         <v>6</v>
       </c>
       <c r="H48" s="13">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="I48" s="14">
         <f t="shared" si="0"/>
-        <v>1020</v>
+        <v>960</v>
       </c>
       <c r="J48" s="14">
         <f t="shared" si="1"/>
-        <v>420</v>
-      </c>
-      <c r="K48" s="15"/>
-      <c r="L48" s="15"/>
-      <c r="M48" s="15"/>
-      <c r="N48" s="16"/>
+        <v>480</v>
+      </c>
+      <c r="K48" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="L48" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M48" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="N48" s="23" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="49" spans="1:14" ht="15">
       <c r="A49" s="8">

--- a/12604714.xlsx
+++ b/12604714.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/af964434807192f7/Documents/cap776^J12604714/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="583" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA4A5898-D4D3-4945-A5CB-35F1DE5993B0}"/>
+  <xr:revisionPtr revIDLastSave="600" documentId="8_{DC97D867-FA8D-4088-A1C9-30DB048EBBE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75E13FD8-8859-4333-8EDD-514BBB95ECBD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -298,6 +298,9 @@
   </si>
   <si>
     <t>today I have 6 class 2 lecture 4 pratical</t>
+  </si>
+  <si>
+    <t>today I have 8 class 5  lecture 3  pratical</t>
   </si>
 </sst>
 </file>
@@ -3112,29 +3115,51 @@
         <v>85</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="15">
+    <row r="49" spans="1:14" ht="28.5">
       <c r="A49" s="8">
         <v>46288</v>
       </c>
-      <c r="B49" s="13"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="13"/>
-      <c r="H49" s="13"/>
-      <c r="I49" s="14" t="str">
+      <c r="B49" s="13">
+        <v>300</v>
+      </c>
+      <c r="C49" s="13">
+        <v>40</v>
+      </c>
+      <c r="D49" s="13">
+        <v>100</v>
+      </c>
+      <c r="E49" s="13">
+        <v>60</v>
+      </c>
+      <c r="F49" s="13">
+        <v>400</v>
+      </c>
+      <c r="G49" s="13">
+        <v>8</v>
+      </c>
+      <c r="H49" s="13">
+        <v>100</v>
+      </c>
+      <c r="I49" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="14" t="str">
+        <v>1000</v>
+      </c>
+      <c r="J49" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="15"/>
-      <c r="L49" s="15"/>
-      <c r="M49" s="15"/>
-      <c r="N49" s="16"/>
+        <v>440</v>
+      </c>
+      <c r="K49" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="L49" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M49" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="N49" s="23" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="50" spans="1:14" ht="15">
       <c r="A50" s="8">
